--- a/CBT_2026_1회/산업안전기사_2026_1회_문항등록.xlsx
+++ b/CBT_2026_1회/산업안전기사_2026_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1683,7 +1683,11 @@
         </is>
       </c>
       <c r="V5" s="32" t="inlineStr"/>
-      <c r="W5" s="32" t="inlineStr"/>
+      <c r="W5" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2026_01_003_stem1.png</t>
+        </is>
+      </c>
       <c r="X5" s="32" t="inlineStr">
         <is>
           <t>금지</t>
@@ -1723,7 +1727,7 @@
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시행규칙 별표6·별표7 — 안전보건표지의 종류와 기본모형&lt;/strong&gt;&lt;br&gt;산업안전보건법 시행규칙 별표6(종류와 형태), 별표7(기본모형). 크기는 안전거리 L 에 따라 정해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금지는 원+사선 · 경고는 삼각 · 지시는 원 · 안내는 사각&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 6&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 7&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시행규칙 별표6·별표7 — 안전보건표지의 종류와 기본모형&lt;/strong&gt;&lt;br&gt;산업안전보건법 시행규칙 별표6(종류와 형태), 별표7(기본모형). 크기는 안전거리 L에 따라 정해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금지는 원+사선 · 경고는 삼각 · 지시는 원 · 안내는 사각&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 6&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 7&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2354,17 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>$B = f ( P \cdot E )$ 에서 &lt;strong&gt;B 는 행동(Behavior)&lt;/strong&gt;이다. 사람의 행동은 &lt;strong&gt;P(개체)&lt;/strong&gt;와 &lt;strong&gt;E(환경)&lt;/strong&gt;의 함수다.&lt;img src="safe_A_2026_01_008_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
+          <t>$B = f ( P \cdot E )$에서 &lt;strong&gt;B는 행동(Behavior)&lt;/strong&gt;이다. 사람의 행동은 &lt;strong&gt;P(개체)&lt;/strong&gt;와 &lt;strong&gt;E(환경)&lt;/strong&gt;의 함수다.&lt;img src="safe_A_2026_01_008_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
-          <t>② 경험은 P 에 드는 요소다.&lt;br&gt;③ 환경은 E 다.&lt;br&gt;④ 인간관계는 E 에 드는 요소다.</t>
+          <t>② 경험은 P에 드는 요소다.&lt;br&gt;③ 환경은 E다.&lt;br&gt;④ 인간관계는 E에 드는 요소다.</t>
         </is>
       </c>
       <c r="AI10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈의 장(場) 이론&lt;/strong&gt;&lt;br&gt;P 를 바꾸는 것이 교육·적성배치, E 를 바꾸는 것이 설비 개선이다. 위험성 감소대책이 공학적 대책을 앞세우는 근거가 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P 는 사람&lt;/u&gt;(연령·성격·지능·소질·경험), &lt;u&gt;E 는 환경&lt;/u&gt;(인간관계·설비·온습도).&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈의 장(場) 이론&lt;/strong&gt;&lt;br&gt;P를 바꾸는 것이 교육·적성배치, E를 바꾸는 것이 설비 개선이다. 위험성 감소대책이 공학적 대책을 앞세우는 근거가 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P는 사람&lt;/u&gt;(연령·성격·지능·소질·경험), &lt;u&gt;E는 환경&lt;/u&gt;(인간관계·설비·온습도).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="Q15" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" s="32" t="inlineStr">
         <is>
@@ -2956,7 +2960,7 @@
       <c r="S15" s="32" t="inlineStr"/>
       <c r="T15" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U15" s="32" t="inlineStr">
@@ -2964,7 +2968,11 @@
           <t>보호구 자율안전확인 고시상 자율안전확인 보호구에 표시하 여야 하는 사항을 모두 고른 것은?</t>
         </is>
       </c>
-      <c r="V15" s="32" t="inlineStr"/>
+      <c r="V15" s="32" t="inlineStr">
+        <is>
+          <t>ㄱ. 모델명   ㄴ. 제조 번호   ㄷ. 사용 기한   ㄹ. 자율안전확인 번호</t>
+        </is>
+      </c>
       <c r="W15" s="32" t="inlineStr"/>
       <c r="X15" s="32" t="inlineStr">
         <is>
@@ -3387,7 +3395,7 @@
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
-          <t>① #2 ~ #3 은 밝기가 더 낮은 작업용이다.&lt;br&gt;③ #6 ~ #8 은 전기로·용광로 등 더 밝은 작업용이다.&lt;br&gt;④ #9 ~ #11 은 아크용접용이다.</t>
+          <t>① #2 ~ #3은 밝기가 더 낮은 작업용이다.&lt;br&gt;③ #6 ~ #8은 전기로·용광로 등 더 밝은 작업용이다.&lt;br&gt;④ #9 ~ #11은 아크용접용이다.</t>
         </is>
       </c>
       <c r="AI18" s="32" t="inlineStr">
@@ -3645,7 +3653,7 @@
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 200 은 경상 20에 10을 곱한 값이다.&lt;br&gt;② 600 은 경상이 10일 때의 값이다.&lt;br&gt;④ 12000 은 자릿수가 한 자리 크다.</t>
+          <t>① 200은 경상 20에 10을 곱한 값이다.&lt;br&gt;② 600은 경상이 10일 때의 값이다.&lt;br&gt;④ 12000은 자릿수가 한 자리 크다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
@@ -3738,7 +3746,11 @@
           <t>A사업장의 현황이 다음과 같을 때 이 사업장의 강도율은?</t>
         </is>
       </c>
-      <c r="V21" s="32" t="inlineStr"/>
+      <c r="V21" s="32" t="inlineStr">
+        <is>
+          <t>근로자수 : 500명&lt;br&gt;연근로시간수 : 2400시간&lt;br&gt;신체장해등급   2급 : 3명,   10급 : 5명&lt;br&gt;의사 진단에 의한 휴업일수 : 1500일</t>
+        </is>
+      </c>
       <c r="W21" s="32" t="inlineStr"/>
       <c r="X21" s="32" t="inlineStr">
         <is>
@@ -3769,17 +3781,17 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>$\text{강도율} = \dfrac{\text{근로손실일수}}{\text{연근로시간수}} \times 1 {,} 000$ 이다. &lt;strong&gt;1,000 근로시간당 근로손실일수&lt;/strong&gt;로, 재해가 얼마나 무겁게 났는지를 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 공식 묶음&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;도수율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해 건수 ÷ 연근로시간수 × &lt;u&gt;1,000,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 자주&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;강도율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근로손실일수 ÷ 연근로시간수 × &lt;u&gt;1,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 무겁게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;연천인율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해자 수 ÷ 상시근로자 수 × &lt;u&gt;1,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000명당 몇 명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;환산도수율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도수율 &lt;u&gt;÷ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평생 재해 건수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;환산강도율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;강도율 &lt;u&gt;× 100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평생 손실일수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;종합재해지수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;√(도수율 × 강도율)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빈도와 강도를 함께&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_019_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>$\text{강도율} = \dfrac{\text{근로손실일수}}{\text{연근로시간수}} \times 1 {,} 000$이다. &lt;strong&gt;1,000 근로시간당 근로손실일수&lt;/strong&gt;로, 재해가 얼마나 무겁게 났는지를 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 공식 묶음&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;도수율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해 건수 ÷ 연근로시간수 × &lt;u&gt;1,000,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 자주&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;강도율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근로손실일수 ÷ 연근로시간수 × &lt;u&gt;1,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 무겁게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;연천인율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해자 수 ÷ 상시근로자 수 × &lt;u&gt;1,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000명당 몇 명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;환산도수율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도수율 &lt;u&gt;÷ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평생 재해 건수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;환산강도율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;강도율 &lt;u&gt;× 100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평생 손실일수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;종합재해지수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;√(도수율 × 강도율)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빈도와 강도를 함께&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_019_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>① 0.22 는 1,000 을 곱하지 않은 값이다.&lt;br&gt;② 2.22 는 자릿수가 한 자리 어긋난 값이다.&lt;br&gt;④ 222.88 은 10,000 이상을 곱했을 때 나오는 값이다.</t>
+          <t>① 0.22는 1,000을 곱하지 않은 값이다.&lt;br&gt;② 2.22는 자릿수가 한 자리 어긋난 값이다.&lt;br&gt;④ 222.88은 10,000 이상을 곱했을 때 나오는 값이다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해율 산정 공식&lt;/strong&gt;&lt;br&gt;사망·영구 전노동불능은 근로손실일수 &lt;strong&gt;7,500일&lt;/strong&gt;, 일시 전노동불능은 &lt;strong&gt;휴업일수 × 300/365&lt;/strong&gt;로 환산한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;도수율은 100만, 강도율은 1,000&lt;/u&gt;. 곱하는 수가 갈림길이다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항에 딸린 「현황」 표는 문제지의 별도 상자에 있어 옮기지 못했다. &lt;u&gt;근로손실일수와 연근로시간수를 식에 넣고 1,000 을 곱한다&lt;/u&gt;는 뼈대만 잡으면 된다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해율 산정 공식&lt;/strong&gt;&lt;br&gt;사망·영구 전노동불능은 근로손실일수 &lt;strong&gt;7,500일&lt;/strong&gt;, 일시 전노동불능은 &lt;strong&gt;휴업일수 × 300/365&lt;/strong&gt;로 환산한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;도수율은 100만, 강도율은 1,000&lt;/u&gt;. 곱하는 수가 갈림길이다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항에 딸린 「현황」 표는 문제지의 별도 상자에 있어 옮기지 못했다. &lt;u&gt;근로손실일수와 연근로시간수를 식에 넣고 1,000을 곱한다&lt;/u&gt;는 뼈대만 잡으면 된다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3996,7 +4008,11 @@
           <t>어떤 결함수를 분석하여 minimal cut set을 구한 결과 다음 과 같았다. 각 기본사상의 발생확률은 qi, i = 1, 2, 3라 할 때, 정상사상의 발생확률함수로 맞는 것은?</t>
         </is>
       </c>
-      <c r="V23" s="32" t="inlineStr"/>
+      <c r="V23" s="32" t="inlineStr">
+        <is>
+          <t>k₁ = [1, 2],   k₂ = [1, 3],   k₃ = [2, 3]</t>
+        </is>
+      </c>
       <c r="W23" s="32" t="inlineStr"/>
       <c r="X23" s="32" t="inlineStr">
         <is>
@@ -4027,17 +4043,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>최소 컷셋이 세 개이므로 정상사상은 &lt;strong&gt;셋 중 어느 하나라도 일어나면&lt;/strong&gt; 발생한다. 포함배제 원리를 쓰되, 두 컷셋의 교집합도 세 컷셋의 교집합도 모두 $q_{1} q_{2} q_{3}$ 이라 계수가 $-3 + 1 =-2$ 로 정리된다.</t>
+          <t>최소 컷셋이 세 개이므로 정상사상은 &lt;strong&gt;셋 중 어느 하나라도 일어나면&lt;/strong&gt; 발생한다. 포함배제 원리를 쓰되, 두 컷셋의 교집합도 세 컷셋의 교집합도 모두 $q_{1} q_{2} q_{3}$이라 계수가 $-3 + 1 =-2$로 정리된다.</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① 같은 항 $q_{1} q_{2}$ 가 두 번 나오고 세 컷셋을 다 더하지도 않았다.&lt;br&gt;② 세 번째 컷셋 $q_{2} q_{3}$ 를 더하지 않고 빼 버렸다.&lt;br&gt;③ 겹치는 부분을 한 번만 뺐다. 컷셋이 세 개면 &lt;strong&gt;2배&lt;/strong&gt;를 빼야 한다.</t>
+          <t>① 같은 항 $q_{1} q_{2}$가 두 번 나오고 세 컷셋을 다 더하지도 않았다.&lt;br&gt;② 세 번째 컷셋 $q_{2} q_{3}$를 더하지 않고 빼 버렸다.&lt;br&gt;③ 겹치는 부분을 한 번만 뺐다. 컷셋이 세 개면 &lt;strong&gt;2배&lt;/strong&gt;를 빼야 한다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;포함배제 원리에 의한 정상사상 확률&lt;/strong&gt;&lt;br&gt;포함배제 원리. 컷셋이 세 개일 때 $P ( A \cup B \cup C ) = P ( A ) + P ( B ) + P ( C ) - P ( AB ) - P ( AC ) - P ( BC ) + P ( \mathrm{ABC} )$. 이 문제처럼 모든 교집합이 같은 값이면 계수가 &lt;u&gt;-3+1 = -2&lt;/u&gt;로 정리된다. 컷셋 두 개면 계수가 -1 이라는 점과 짝지어 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 컷셋 &lt;u&gt;둘&lt;/u&gt;이면 겹침을 &lt;u&gt;1번&lt;/u&gt;, &lt;u&gt;셋&lt;/u&gt;이면 &lt;u&gt;2배&lt;/u&gt;를 뺀다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;포함배제 원리에 의한 정상사상 확률&lt;/strong&gt;&lt;br&gt;포함배제 원리. 컷셋이 세 개일 때 $P ( A \cup B \cup C ) = P ( A ) + P ( B ) + P ( C ) - P ( AB ) - P ( AC ) - P ( BC ) + P ( \mathrm{ABC} )$. 이 문제처럼 모든 교집합이 같은 값이면 계수가 &lt;u&gt;-3+1 = -2&lt;/u&gt;로 정리된다. 컷셋 두 개면 계수가 -1이라는 점과 짝지어 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 컷셋 &lt;u&gt;둘&lt;/u&gt;이면 겹침을 &lt;u&gt;1번&lt;/u&gt;, &lt;u&gt;셋&lt;/u&gt;이면 &lt;u&gt;2배&lt;/u&gt;를 뺀다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4271,11 @@
         </is>
       </c>
       <c r="V25" s="32" t="inlineStr"/>
-      <c r="W25" s="32" t="inlineStr"/>
+      <c r="W25" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2026_01_023_stem1.png</t>
+        </is>
+      </c>
       <c r="X25" s="32" t="inlineStr">
         <is>
           <t>(XI, X2)</t>
@@ -4295,7 +4315,7 @@
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소 컷셋과 최소 패스셋&lt;/strong&gt;&lt;br&gt;컷셋과 패스셋. &lt;u&gt;최소 컷셋은 시스템의 위험성&lt;/u&gt;(그것만 무너지면 끝나는 지점), &lt;u&gt;최소 패스셋은 시스템의 안전성&lt;/u&gt;(그것만 살아 있으면 버티는 지점)을 나타낸다. 최소 컷셋의 &lt;u&gt;크기가 작을수록 취약&lt;/u&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷셋은 위험성, 패스셋은 안전성&lt;/u&gt;. 컷셋이 작을수록 취약하다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 FT 그림은 이 책에 옮기지 못했다. 이런 유형은 &lt;u&gt;「부울 대수로 전개 → 흡수법칙으로 정리 → 남은 항이 최소 컷셋」&lt;/u&gt;이라는 절차만 익혀 두면 그림이 달라져도 풀린다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소 컷셋과 최소 패스셋&lt;/strong&gt;&lt;br&gt;컷셋과 패스셋. &lt;u&gt;최소 컷셋은 시스템의 위험성&lt;/u&gt;(그것만 무너지면 끝나는 지점), &lt;u&gt;최소 패스셋은 시스템의 안전성&lt;/u&gt;(그것만 살아 있으면 버티는 지점)을 나타낸다. 최소 컷셋의 &lt;u&gt;크기가 작을수록 취약&lt;/u&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷셋은 위험성, 패스셋은 안전성&lt;/u&gt;. 컷셋이 작을수록 취약하다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 FT 그림은 이 책에 옮기지 못했다. 이런 유형은 &lt;u&gt;「부울 대수로 전개 → 흡수법칙으로 정리 → 남은 항이 최소 컷셋」&lt;/u&gt;이라는 절차만 익혀 두면 그림이 달라져도 풀린다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4493,10 +4513,14 @@
       </c>
       <c r="U27" s="32" t="inlineStr">
         <is>
-          <t>1 sone에 관한 설명으로 ( ) 에 알맞은 수치는?</t>
-        </is>
-      </c>
-      <c r="V27" s="32" t="inlineStr"/>
+          <t>1 sone에 관한 설명으로 ( )에 알맞은 수치는?</t>
+        </is>
+      </c>
+      <c r="V27" s="32" t="inlineStr">
+        <is>
+          <t>1 sone : ( ㄱ )Hz, ( ㄴ )dB의 음압수준을 가진 순음의 크기</t>
+        </is>
+      </c>
       <c r="W27" s="32" t="inlineStr"/>
       <c r="X27" s="32" t="inlineStr">
         <is>
@@ -4527,17 +4551,17 @@
       </c>
       <c r="AG27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1 sone 은 1,000 [Hz] 순음이 40 [dB] 일 때의 음량&lt;/strong&gt;으로 정의한다. 「천 헤르츠, 사십 데시벨」을 묶어 외운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;phon 과 sone&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;phon&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;sone&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;40&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음 40 [dB]&lt;/u&gt;가 기준&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;50&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;phon 이 10 오르면 sone 은 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;60&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;70&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;80&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;16&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1 sone은 1,000 [Hz] 순음이 40 [dB] 일 때의 음량&lt;/strong&gt;으로 정의한다. 「천 헤르츠, 사십 데시벨」을 묶어 외운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;phon과 sone&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;phon&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;sone&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;40&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음 40 [dB]&lt;/u&gt;가 기준&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;50&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;phon이 10 오르면 sone은 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;60&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;70&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;80&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;16&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>① 40 [dB] 이 아니라 1 [dB] 로 잡았다.&lt;br&gt;② 주파수와 음압 둘 다 틀렸다.&lt;br&gt;④ 기준 주파수를 4,000 [Hz] 로 잡았다. 4,000 [Hz] 는 사람 귀가 가장 예민한 대역이지 sone 의 기준이 아니다.</t>
+          <t>① 40 [dB]이 아니라 1 [dB]로 잡았다.&lt;br&gt;② 주파수와 음압 둘 다 틀렸다.&lt;br&gt;④ 기준 주파수를 4,000 [Hz]로 잡았다. 4,000 [Hz]는 사람 귀가 가장 예민한 대역이지 sone의 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음량의 척도 — phon 과 sone&lt;/strong&gt;&lt;br&gt;음량의 두 척도. &lt;u&gt;phon 은 1,000 [Hz] 순음과 같게 들리는 음압수준(dB)&lt;/u&gt;이고, &lt;u&gt;sone 은 그 크기를 비율로 나타낸 값&lt;/u&gt;이다. 관계식은 $\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$ 이며, &lt;u&gt;phon 이 10 오를 때마다 sone 은 2배&lt;/u&gt;가 된다. 40 phon = 1 sone 이 출발점이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Hz] · 40 [dB] = 1 sone&lt;/u&gt;. phon 10 오르면 sone 2배.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음량의 척도 — phon과 sone&lt;/strong&gt;&lt;br&gt;음량의 두 척도. &lt;u&gt;phon은 1,000 [Hz] 순음과 같게 들리는 음압수준(dB)&lt;/u&gt;이고, &lt;u&gt;sone은 그 크기를 비율로 나타낸 값&lt;/u&gt;이다. 관계식은 $\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$이며, &lt;u&gt;phon이 10 오를 때마다 sone은 2배&lt;/u&gt;가 된다. 40 phon = 1 sone이 출발점이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Hz] · 40 [dB] = 1 sone&lt;/u&gt;. phon 10 오르면 sone 2배.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
@@ -4609,7 +4633,7 @@
       <c r="S28" s="32" t="inlineStr"/>
       <c r="T28" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2022.03.05 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1 | 분류 미상</t>
+          <t>원본 시행일 2022.03.05 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2 | 분류 미상</t>
         </is>
       </c>
       <c r="U28" s="32" t="inlineStr">
@@ -4617,7 +4641,11 @@
           <t>인간공학적 연구에 사용되는 기준 척도의 요건 중 다음 설 명에 해당하는 것은?</t>
         </is>
       </c>
-      <c r="V28" s="32" t="inlineStr"/>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>기준 척도는 측정하고자 하는 변수 외의 다른 변수들의 영향을 받아서는 안된다.</t>
+        </is>
+      </c>
       <c r="W28" s="32" t="inlineStr"/>
       <c r="X28" s="32" t="inlineStr">
         <is>
@@ -4782,12 +4810,12 @@
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① 명료도 지수(AI)는 각 주파수 대역의 신호 대 잡음비에 가중치를 매겨 더한 값이다. 잡음만이 아니라 &lt;strong&gt;신호와 잡음의 관계&lt;/strong&gt;를 본다.&lt;br&gt;③ 이해도 점수는 실제로 말을 들려주고 &lt;strong&gt;몇 [%] 를 알아들었는지&lt;/strong&gt; 재는 값이다.&lt;br&gt;④ 「통화 공진 수준」이라는 척도는 없다.</t>
+          <t>① 명료도 지수(AI)는 각 주파수 대역의 신호 대 잡음비에 가중치를 매겨 더한 값이다. 잡음만이 아니라 &lt;strong&gt;신호와 잡음의 관계&lt;/strong&gt;를 본다.&lt;br&gt;③ 이해도 점수는 실제로 말을 들려주고 &lt;strong&gt;몇 [%]를 알아들었는지&lt;/strong&gt; 재는 값이다.&lt;br&gt;④ 「통화 공진 수준」이라는 척도는 없다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;통화이해도 척도&lt;/strong&gt;&lt;br&gt;네 가지. &lt;u&gt;명료도 지수(AI) · 통화 간섭 수준(PSIL) · 이해도 점수 · 소음기준곡선(NC)&lt;/u&gt;. 무엇을 재는지로 가른다 — &lt;u&gt;PSIL 은 잡음 쪽&lt;/u&gt;, &lt;u&gt;AI 는 신호 대 잡음비&lt;/u&gt;, &lt;u&gt;이해도 점수는 사람이 실제로 알아들은 비율&lt;/u&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PSIL 은 잡음, AI 는 신호 대 잡음비, 이해도 점수는 실제로 알아들은 비율&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;통화이해도 척도&lt;/strong&gt;&lt;br&gt;네 가지. &lt;u&gt;명료도 지수(AI) · 통화 간섭 수준(PSIL) · 이해도 점수 · 소음기준곡선(NC)&lt;/u&gt;. 무엇을 재는지로 가른다 — &lt;u&gt;PSIL은 잡음 쪽&lt;/u&gt;, &lt;u&gt;AI는 신호 대 잡음비&lt;/u&gt;, &lt;u&gt;이해도 점수는 사람이 실제로 알아들은 비율&lt;/u&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PSIL은 잡음, AI는 신호 대 잡음비, 이해도 점수는 실제로 알아들은 비율&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4939,7 @@
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>② FHA(결함위험분석)는 &lt;strong&gt;설계·개발 단계&lt;/strong&gt;에서 여러 하청업체가 나눠 만든 서브시스템이 서로 맞물릴 때의 위험을 본다.&lt;br&gt;③ OHA(운용위험분석)는 &lt;strong&gt;운용 단계&lt;/strong&gt;에서 사용·정비·수송 중의 위험을 본다.&lt;br&gt;④ SHA(시스템위험분석)는 서브시스템이 하나로 합쳐진 뒤의 위험을 본다. PHA 보다 뒤다.</t>
+          <t>② FHA(결함위험분석)는 &lt;strong&gt;설계·개발 단계&lt;/strong&gt;에서 여러 하청업체가 나눠 만든 서브시스템이 서로 맞물릴 때의 위험을 본다.&lt;br&gt;③ OHA(운용위험분석)는 &lt;strong&gt;운용 단계&lt;/strong&gt;에서 사용·정비·수송 중의 위험을 본다.&lt;br&gt;④ SHA(시스템위험분석)는 서브시스템이 하나로 합쳐진 뒤의 위험을 본다. PHA보다 뒤다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
@@ -5035,7 +5063,7 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>PHA 의 네 범주는 &lt;strong&gt;파국적 · 중대 · 한계적 · 무시가능&lt;/strong&gt;이다. 「수용가능」이 아니라 &lt;strong&gt;무시가능(negligible)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA 의 위험성 4범주&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범주&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파국적 catastrophic&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사망 또는 시스템 완전 손실&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계 변경 필수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중대 critical&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심각한 부상, 시스템 중대 손상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;즉시 시정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한계적 marginal&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경미한 부상, 제어 가능&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;통제하며 운용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무시가능 negligible&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부상이나 손상이 없음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조치 불필요&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>PHA의 네 범주는 &lt;strong&gt;파국적 · 중대 · 한계적 · 무시가능&lt;/strong&gt;이다. 「수용가능」이 아니라 &lt;strong&gt;무시가능(negligible)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA의 위험성 4범주&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범주&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파국적 catastrophic&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사망 또는 시스템 완전 손실&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계 변경 필수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중대 critical&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심각한 부상, 시스템 중대 손상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;즉시 시정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한계적 marginal&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경미한 부상, 제어 가능&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;통제하며 운용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무시가능 negligible&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부상이나 손상이 없음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조치 불필요&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
@@ -5045,7 +5073,7 @@
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예비위험분석(PHA)의 위험성 범주&lt;/strong&gt;&lt;br&gt;PHA 는 &lt;strong&gt;구상 단계&lt;/strong&gt;에서 하는 최초의 위험분석이라, 위험을 네 등급으로 크게 훑는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 「&lt;u&gt;파 · 중 · 한 · 무&lt;/u&gt;」 — 넷째는 수용가능이 아니라 &lt;u&gt;무시가능&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;예비위험분석(PHA)의 위험성 범주&lt;/strong&gt;&lt;br&gt;PHA는 &lt;strong&gt;구상 단계&lt;/strong&gt;에서 하는 최초의 위험분석이라, 위험을 네 등급으로 크게 훑는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 「&lt;u&gt;파 · 중 · 한 · 무&lt;/u&gt;」 — 넷째는 수용가능이 아니라 &lt;u&gt;무시가능&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5164,17 +5192,17 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>타이어는 &lt;strong&gt;하나만 터져도 차가 못 간다&lt;/strong&gt;므로 &lt;strong&gt;직렬&lt;/strong&gt;이다. 하나의 신뢰도가 $1 - 0.01 = 0.99$ 이고 넷이 직렬이므로 $0.99^{4} \fallingdotseq 0.96$ 이다.&lt;img src="safe_A_2026_01_030_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
+          <t>타이어는 &lt;strong&gt;하나만 터져도 차가 못 간다&lt;/strong&gt;므로 &lt;strong&gt;직렬&lt;/strong&gt;이다. 하나의 신뢰도가 $1 - 0.01 = 0.99$이고 넷이 직렬이므로 $0.99^{4} \fallingdotseq 0.96$이다.&lt;img src="safe_A_2026_01_030_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 0.91 은 지수를 잘못 잡았을 때 나온다.&lt;br&gt;② 0.93 도 계산과 맞지 않는다.&lt;br&gt;④ 0.99 는 타이어 한 개의 신뢰도다. 넷을 곱하는 것을 잊으면 이 답을 고른다.</t>
+          <t>① 0.91은 지수를 잘못 잡았을 때 나온다.&lt;br&gt;② 0.93 도 계산과 맞지 않는다.&lt;br&gt;④ 0.99는 타이어 한 개의 신뢰도다. 넷을 곱하는 것을 잊으면 이 답을 고른다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직렬·병렬 신뢰도&lt;/strong&gt;&lt;br&gt;직렬은 $R = R_{1} R_{2} \cdots R_{n}$ 으로 부품이 늘수록 나빠지고, 병렬은 $R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} ) \cdots$ 로 늘수록 좋아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나만 고장 나도 멈추면 직렬&lt;/u&gt;, 하나가 고장 나도 버티면 병렬.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;직렬·병렬 신뢰도&lt;/strong&gt;&lt;br&gt;직렬은 $R = R_{1} R_{2} \cdots R_{n}$으로 부품이 늘수록 나빠지고, 병렬은 $R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} ) \cdots$로 늘수록 좋아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나만 고장 나도 멈추면 직렬&lt;/u&gt;, 하나가 고장 나도 버티면 병렬.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5293,17 +5321,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MTTR(Mean Time To Repair, 평균수리시간)&lt;/strong&gt;이다. &lt;strong&gt;보전도&lt;/strong&gt;를 나타내는 지표이며, 짧을수록 좋다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;신뢰성·보전성 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 나타내나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTBF&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장과 고장 사이의 평균 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신뢰도&lt;/u&gt; — 수리하며 쓰는 설비&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTTF&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장까지의 평균 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신뢰도&lt;/u&gt; — 수리하지 않는 부품&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTTR&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평균 수리시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보전도&lt;/u&gt; — 짧을수록 좋다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;가용도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;MTBF ÷ (MTBF + MTTR)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;쓸 수 있는 시간의 비율&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_031_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR 의 관계&lt;/em&gt;</t>
+          <t>&lt;strong&gt;MTTR(Mean Time To Repair, 평균수리시간)&lt;/strong&gt;이다. &lt;strong&gt;보전도&lt;/strong&gt;를 나타내는 지표이며, 짧을수록 좋다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;신뢰성·보전성 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 나타내나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTBF&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장과 고장 사이의 평균 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신뢰도&lt;/u&gt; — 수리하며 쓰는 설비&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTTF&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장까지의 평균 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신뢰도&lt;/u&gt; — 수리하지 않는 부품&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;MTTR&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;평균 수리시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보전도&lt;/u&gt; — 짧을수록 좋다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;가용도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;MTBF ÷ (MTBF + MTTR)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;쓸 수 있는 시간의 비율&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_031_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR의 관계&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① MTBF(Mean Time Between Failures)는 &lt;strong&gt;고장과 고장 사이의 평균 시간&lt;/strong&gt;으로, 수리하며 쓰는 설비의 신뢰도 지표다.&lt;br&gt;③ MTTF(Mean Time To Failure)는 &lt;strong&gt;고장까지의 평균 시간&lt;/strong&gt;으로, 수리하지 않고 버리는 부품의 신뢰도 지표다.&lt;br&gt;④ MTBP 라는 지표는 없다.</t>
+          <t>① MTBF(Mean Time Between Failures)는 &lt;strong&gt;고장과 고장 사이의 평균 시간&lt;/strong&gt;으로, 수리하며 쓰는 설비의 신뢰도 지표다.&lt;br&gt;③ MTTF(Mean Time To Failure)는 &lt;strong&gt;고장까지의 평균 시간&lt;/strong&gt;으로, 수리하지 않고 버리는 부품의 신뢰도 지표다.&lt;br&gt;④ MTBP라는 지표는 없다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;신뢰성·보전성 지표와 가용도&lt;/strong&gt;&lt;br&gt;신뢰성과 보전성의 구분. &lt;u&gt;신뢰도는 「잘 고장 나지 않는가」(MTBF · MTTF)&lt;/u&gt;, &lt;u&gt;보전도는 「빨리 고칠 수 있는가」(MTTR)&lt;/u&gt;다. 둘을 합친 것이 가용도 $A = \mathrm{MTBF} / ( \mathrm{MTBF} + \mathrm{MTTR} )$ 이며, $\mathrm{MTBF} = \mathrm{MTTF} + \mathrm{MTTR}$ 의 관계도 함께 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTBF·MTTF 는 신뢰도, MTTR 는 보전도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;신뢰성·보전성 지표와 가용도&lt;/strong&gt;&lt;br&gt;신뢰성과 보전성의 구분. &lt;u&gt;신뢰도는 「잘 고장 나지 않는가」(MTBF · MTTF)&lt;/u&gt;, &lt;u&gt;보전도는 「빨리 고칠 수 있는가」(MTTR)&lt;/u&gt;다. 둘을 합친 것이 가용도 $A = \mathrm{MTBF} / ( \mathrm{MTBF} + \mathrm{MTTR} )$이며, $\mathrm{MTBF} = \mathrm{MTTF} + \mathrm{MTTR}$의 관계도 함께 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTBF·MTTF는 신뢰도, MTTR는 보전도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="Q34" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
@@ -5383,7 +5411,7 @@
       <c r="S34" s="32" t="inlineStr"/>
       <c r="T34" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U34" s="32" t="inlineStr">
@@ -5391,7 +5419,11 @@
           <t>근골격계질환 작업분석 및 평가 방법인 OWAS의 평가요소 를 모두 고른 것은?</t>
         </is>
       </c>
-      <c r="V34" s="32" t="inlineStr"/>
+      <c r="V34" s="32" t="inlineStr">
+        <is>
+          <t>ㄱ. 상지   ㄴ. 무게(하중)   ㄷ. 하지   ㄹ. 허리</t>
+        </is>
+      </c>
       <c r="W34" s="32" t="inlineStr"/>
       <c r="X34" s="32" t="inlineStr">
         <is>
@@ -5422,12 +5454,12 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>OWAS 는 &lt;strong&gt;허리 · 팔(상지) · 다리(하지) · 하중(무게)&lt;/strong&gt; 네 가지를 코드로 매겨 자세를 평가한다. 네 요소를 모두 보므로 정답은 ④다. 사진이나 동영상으로 자세를 찍어 코드만 매기면 되므로 &lt;strong&gt;현장에서 빠르게 쓸 수 있다&lt;/strong&gt;는 것이 이 기법의 장점이다.</t>
+          <t>OWAS는 &lt;strong&gt;허리 · 팔(상지) · 다리(하지) · 하중(무게)&lt;/strong&gt; 네 가지를 코드로 매겨 자세를 평가한다. 네 요소를 모두 보므로 정답은 ④다. 사진이나 동영상으로 자세를 찍어 코드만 매기면 되므로 &lt;strong&gt;현장에서 빠르게 쓸 수 있다&lt;/strong&gt;는 것이 이 기법의 장점이다.</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
         <is>
-          <t>① 두 요소만으로는 OWAS 의 평가가 성립하지 않는다.&lt;br&gt;② 하중을 빼면 무거운 물건을 드는 작업의 부담을 놓친다.&lt;br&gt;③ 허리를 빼면 근골격계 부담의 핵심을 놓친다.</t>
+          <t>① 두 요소만으로는 OWAS의 평가가 성립하지 않는다.&lt;br&gt;② 하중을 빼면 무거운 물건을 드는 작업의 부담을 놓친다.&lt;br&gt;③ 허리를 빼면 근골격계 부담의 핵심을 놓친다.</t>
         </is>
       </c>
       <c r="AI34" s="32" t="inlineStr">
@@ -5646,7 +5678,7 @@
       </c>
       <c r="U36" s="32" t="inlineStr">
         <is>
-          <t>태양광선이 내리쬐는 옥외장소의 자연습구온도 20℃, 흑구 온도 18℃, 건구온도 30℃ 일 때 습구흑구온도지수(WBGT) 는?</t>
+          <t>태양광선이 내리쬐는 옥외장소의 자연습구온도 20℃, 흑구 온도 18℃, 건구온도 30℃ 일 때 습구흑구온도지수(WBGT)는?</t>
         </is>
       </c>
       <c r="V36" s="32" t="inlineStr"/>
@@ -5680,17 +5712,17 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;햇볕이 있는 옥외&lt;/strong&gt;는 건구온도까지 넣는 식을 쓴다. $\mathrm{WBGT} = 0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$ 이므로 $0.7 \times 20 + 0.2 \times 18 + 0.1 \times 30 = 14 + 3.6 + 3 = 20.6$ [℃] 다.</t>
+          <t>&lt;strong&gt;햇볕이 있는 옥외&lt;/strong&gt;는 건구온도까지 넣는 식을 쓴다. $\mathrm{WBGT} = 0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$이므로 $0.7 \times 20 + 0.2 \times 18 + 0.1 \times 30 = 14 + 3.6 + 3 = 20.6$ [℃]다.</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>② 옥내 식($0.7 \times \text{습구} + 0.3 \times \text{흑구}$)을 쓰면 20.6 이 아닌 다른 값이 나온다.&lt;br&gt;③ 계수를 잘못 잡았을 때 나오는 값이다.&lt;br&gt;④ 건구온도 30 에 가까운 값으로, 가중치를 무시하고 단순 평균했을 때 나온다.</t>
+          <t>② 옥내 식($0.7 \times \text{습구} + 0.3 \times \text{흑구}$)을 쓰면 20.6이 아닌 다른 값이 나온다.&lt;br&gt;③ 계수를 잘못 잡았을 때 나오는 값이다.&lt;br&gt;④ 건구온도 30에 가까운 값으로, 가중치를 무시하고 단순 평균했을 때 나온다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;WBGT 두 가지 식. &lt;u&gt;옥내 또는 햇볕 없는 옥외 : 0.7 자연습구 + 0.3 흑구&lt;/u&gt;, &lt;u&gt;햇볕 있는 옥외 : 0.7 자연습구 + 0.2 흑구 + 0.1 건구&lt;/u&gt;. &lt;u&gt;자연습구의 가중치 0.7 은 어느 경우에나 같고, 건구는 햇볕이 있을 때만 0.1 로 들어간다&lt;/u&gt;는 점이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연습구 0.7 은 언제나 같고, 건구 0.1 은 햇볕이 있을 때만&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;WBGT 두 가지 식. &lt;u&gt;옥내 또는 햇볕 없는 옥외 : 0.7 자연습구 + 0.3 흑구&lt;/u&gt;, &lt;u&gt;햇볕 있는 옥외 : 0.7 자연습구 + 0.2 흑구 + 0.1 건구&lt;/u&gt;. &lt;u&gt;자연습구의 가중치 0.7은 어느 경우에나 같고, 건구는 햇볕이 있을 때만 0.1로 들어간다&lt;/u&gt;는 점이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연습구 0.7은 언제나 같고, 건구 0.1은 햇볕이 있을 때만&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5809,17 +5841,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Other than 은 「완전한 대체」&lt;/strong&gt;, 곧 의도한 것과 &lt;strong&gt;전혀 다른 것이 일어남&lt;/strong&gt;을 뜻한다. 「기타 환경적인 요인」이 아니다.</t>
+          <t>&lt;strong&gt;Other than은 「완전한 대체」&lt;/strong&gt;, 곧 의도한 것과 &lt;strong&gt;전혀 다른 것이 일어남&lt;/strong&gt;을 뜻한다. 「기타 환경적인 요인」이 아니다.</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① Part of 는 성질상의 감소로, 일부만 이루어진 상태를 뜻한다.&lt;br&gt;② As well as 는 성질상의 증가로, 의도한 것에 더해 다른 것이 함께 일어남을 뜻한다.&lt;br&gt;④ More/Less 는 정량적인 증가 또는 감소를 뜻한다.</t>
+          <t>① Part of는 성질상의 감소로, 일부만 이루어진 상태를 뜻한다.&lt;br&gt;② As well as는 성질상의 증가로, 의도한 것에 더해 다른 것이 함께 일어남을 뜻한다.&lt;br&gt;④ More/Less는 정량적인 증가 또는 감소를 뜻한다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HAZOP 의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;u&gt;No/Not(설계 의도의 완전한 부정) · More/Less(양적 증감) · As well as(질적 증가) · Part of(질적 감소) · Reverse(설계 의도와 반대) · Other than(완전한 대체)&lt;/u&gt;. &lt;u&gt;양적인 것은 More/Less, 질적인 것은 As well as / Part of&lt;/u&gt;로 짝지어 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;양은 More/Less, 질은 As well as / Part of&lt;/u&gt;. Other than 은 완전한 대체.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;HAZOP의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;u&gt;No/Not(설계 의도의 완전한 부정) · More/Less(양적 증감) · As well as(질적 증가) · Part of(질적 감소) · Reverse(설계 의도와 반대) · Other than(완전한 대체)&lt;/u&gt;. &lt;u&gt;양적인 것은 More/Less, 질적인 것은 As well as / Part of&lt;/u&gt;로 짝지어 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;양은 More/Less, 질은 As well as / Part of&lt;/u&gt;. Other than은 완전한 대체.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6228,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 &lt;strong&gt;복잡하고 대형화된 시스템&lt;/strong&gt;의 신뢰성과 안전성을 분석하는 기법이다. 정상사상을 먼저 정하고 그 원인을 거꾸로 파고드는 &lt;strong&gt;연역적·하향식(top-down)&lt;/strong&gt; 기법이며, 각 사상의 확률을 알면 &lt;strong&gt;정량적 계산도 된다&lt;/strong&gt;.</t>
+          <t>FTA는 &lt;strong&gt;복잡하고 대형화된 시스템&lt;/strong&gt;의 신뢰성과 안전성을 분석하는 기법이다. 정상사상을 먼저 정하고 그 원인을 거꾸로 파고드는 &lt;strong&gt;연역적·하향식(top-down)&lt;/strong&gt; 기법이며, 각 사상의 확률을 알면 &lt;strong&gt;정량적 계산도 된다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6206,7 +6238,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 와 FMEA 의 대비&lt;/strong&gt;&lt;br&gt;&lt;u&gt;FTA 는 연역적·하향식·정량 가능&lt;/u&gt;, &lt;u&gt;FMEA 는 귀납적·상향식·정성 중심&lt;/u&gt;이다. FTA 는 1962년 벨연구소가 미니트맨 미사일의 발사 제어 시스템을 분석하며 만든 기법이라, 처음부터 &lt;u&gt;크고 복잡한 시스템&lt;/u&gt;을 겨냥하고 있었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 연역·하향·정량 가능, FMEA 는 귀납·상향·정성&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA와 FMEA의 대비&lt;/strong&gt;&lt;br&gt;&lt;u&gt;FTA는 연역적·하향식·정량 가능&lt;/u&gt;, &lt;u&gt;FMEA는 귀납적·상향식·정성 중심&lt;/u&gt;이다. FTA는 1962년 벨연구소가 미니트맨 미사일의 발사 제어 시스템을 분석하며 만든 기법이라, 처음부터 &lt;u&gt;크고 복잡한 시스템&lt;/u&gt;을 겨냥하고 있었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 연역·하향·정량 가능, FMEA는 귀납·상향·정성&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6323,7 @@
       </c>
       <c r="U41" s="32" t="inlineStr">
         <is>
-          <t>반사경 없이 모든 방향으로 빛을 발하는 점광원에서 3m 떨 어진 곳의 조도가 300lux라면 2m 떨어진 곳에서 조도(lux) 는?</t>
+          <t>반사경 없이 모든 방향으로 빛을 발하는 점광원에서 3m 떨 어진 곳의 조도가 300lux라면 2m 떨어진 곳에서 조도(lux)는?</t>
         </is>
       </c>
       <c r="V41" s="32" t="inlineStr"/>
@@ -6325,12 +6357,12 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>조도는 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt; 한다. 광도 $I = 300 \times 3^{2} = 2 {,} 700$ [cd] 이므로 2 [m] 지점은 $2 {,} 700 / 2^{2} = 675$ [lux] 다.</t>
+          <t>조도는 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt;한다. 광도 $I = 300 \times 3^{2} = 2 {,} 700$ [cd]이므로 2 [m] 지점은 $2 {,} 700 / 2^{2} = 675$ [lux]다.</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① 375 는 거리에 단순 반비례한다고 보았을 때에 가깝다.&lt;br&gt;③ 875 는 계산과 맞지 않는다.&lt;br&gt;④ 975 도 계산과 맞지 않는다.</t>
+          <t>① 375는 거리에 단순 반비례한다고 보았을 때에 가깝다.&lt;br&gt;③ 875는 계산과 맞지 않는다.&lt;br&gt;④ 975 도 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
@@ -6464,7 +6496,7 @@
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;광속 · 광도 · 조도 · 휘도&lt;/strong&gt;&lt;br&gt;조도는 $E = I / r^{2}$ 로 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광도는 나가는 쪽, 조도는 닿는 쪽, 휘도는 되돌아오는 쪽&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;광속 · 광도 · 조도 · 휘도&lt;/strong&gt;&lt;br&gt;조도는 $E = I / r^{2}$로 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광도는 나가는 쪽, 조도는 닿는 쪽, 휘도는 되돌아오는 쪽&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6685,13 +6717,13 @@
       <c r="W44" s="32" t="inlineStr"/>
       <c r="X44" s="32" t="inlineStr">
         <is>
-          <t>탁상용 연삭기에서 숫돌과 작업 받침대의 간격이 5mm 이다.</t>
+          <t>탁상용 연삭기에서 숫돌과 작업 받침대의 간격이 5mm이다.</t>
         </is>
       </c>
       <c r="Y44" s="32" t="inlineStr"/>
       <c r="Z44" s="32" t="inlineStr">
         <is>
-          <t>덮개 재료의 인장강도는 224MPa 이다.</t>
+          <t>덮개 재료의 인장강도는 224MPa이다.</t>
         </is>
       </c>
       <c r="AA44" s="32" t="inlineStr"/>
@@ -6717,7 +6749,7 @@
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 숫돌과 작업 받침대(워크레스트)의 간격은 &lt;strong&gt;3 [mm] 이내&lt;/strong&gt; 여야 한다. 5 [mm] 는 넓어서 공작물이 끼어 들어간다.&lt;br&gt;② 덮개 재료의 인장강도는 &lt;strong&gt;274.5 [MPa] 이상&lt;/strong&gt; 이어야 한다. 224 [MPa] 는 모자란다.&lt;br&gt;③ 숫돌을 &lt;strong&gt;교체한 뒤에는 3분 이상&lt;/strong&gt; 시험운전을 해야 한다. 2분으로는 모자란다.</t>
+          <t>① 숫돌과 작업 받침대(워크레스트)의 간격은 &lt;strong&gt;3 [mm] 이내&lt;/strong&gt; 여야 한다. 5 [mm]는 넓어서 공작물이 끼어 들어간다.&lt;br&gt;② 덮개 재료의 인장강도는 &lt;strong&gt;274.5 [MPa] 이상&lt;/strong&gt; 이어야 한다. 224 [MPa]는 모자란다.&lt;br&gt;③ 숫돌을 &lt;strong&gt;교체한 뒤에는 3분 이상&lt;/strong&gt; 시험운전을 해야 한다. 2분으로는 모자란다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
@@ -6846,7 +6878,7 @@
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
-          <t>① 30 [mm] 는 1/5 로, 기준에 못 미친다.&lt;br&gt;③ 60 [mm] 는 기준(50 [mm])보다 크므로 「이상」 조건은 만족하나 문제가 묻는 &lt;strong&gt;최소값&lt;/strong&gt;이 아니다.&lt;br&gt;④ 90 [mm] 도 마찬가지로 최소값이 아니다.</t>
+          <t>① 30 [mm]는 1/5로, 기준에 못 미친다.&lt;br&gt;③ 60 [mm]는 기준(50 [mm])보다 크므로 「이상」 조건은 만족하나 문제가 묻는 &lt;strong&gt;최소값&lt;/strong&gt;이 아니다.&lt;br&gt;④ 90 [mm] 도 마찬가지로 최소값이 아니다.</t>
         </is>
       </c>
       <c r="AI45" s="32" t="inlineStr">
@@ -7068,7 +7100,11 @@
           <t>보기와 같은 기계요소가 단독으로 발생시키는 위험점은?</t>
         </is>
       </c>
-      <c r="V47" s="32" t="inlineStr"/>
+      <c r="V47" s="32" t="inlineStr">
+        <is>
+          <t>밀링커터, 둥근톱날</t>
+        </is>
+      </c>
       <c r="W47" s="32" t="inlineStr"/>
       <c r="X47" s="32" t="inlineStr">
         <is>
@@ -7228,12 +7264,12 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>$\text{안전율} = \dfrac{\text{극한강도}}{\text{허용응력}}$ 이므로 $\text{허용응력} = 250 / 4 = 62.5$ [N/mm²] 다.</t>
+          <t>$\text{안전율} = \dfrac{\text{극한강도}}{\text{허용응력}}$이므로 $\text{허용응력} = 250 / 4 = 62.5$ [N/mm²]다.</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
         <is>
-          <t>① 42.5 는 계산이 맞지 않는다.&lt;br&gt;③ 82.5 는 3으로 나눈 값에 가깝다.&lt;br&gt;④ 102.5 는 2.44 로 나눈 값으로 안전율 4와 맞지 않는다.</t>
+          <t>① 42.5는 계산이 맞지 않는다.&lt;br&gt;③ 82.5는 3으로 나눈 값에 가깝다.&lt;br&gt;④ 102.5는 2.44로 나눈 값으로 안전율 4와 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI48" s="32" t="inlineStr">
@@ -7471,7 +7507,7 @@
       <c r="AA50" s="32" t="inlineStr"/>
       <c r="AB50" s="32" t="inlineStr">
         <is>
-          <t>방호장치는 릴레이, 리미트 스위치 등의 전기부품의 고 장, 전원전압의 변동 및 정전에 의해 슬라이드가 불시에 동작하지 않아야 하며, 사용전원전압의 ±(100분의 10) 의 변동에 대하여 정상으로 작동되어야 한다.</t>
+          <t>방호장치는 릴레이, 리미트 스위치 등의 전기부품의 고 장, 전원전압의 변동 및 정전에 의해 슬라이드가 불시에 동작하지 않아야 하며, 사용전원전압의 ±(100분의 10)의 변동에 대하여 정상으로 작동되어야 한다.</t>
         </is>
       </c>
       <c r="AC50" s="32" t="inlineStr"/>
@@ -7486,7 +7522,7 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>전원전압 변동에 대한 허용 범위는 &lt;strong&gt;±(100분의 20)&lt;/strong&gt;이다. 100분의 10 이 아니다. 현장의 전압은 생각보다 크게 흔들리므로, 방호장치가 그 정도 변동에는 흔들림 없이 작동해야 한다는 뜻이다.</t>
+          <t>전원전압 변동에 대한 허용 범위는 &lt;strong&gt;±(100분의 20)&lt;/strong&gt;이다. 100분의 10이 아니다. 현장의 전압은 생각보다 크게 흔들리므로, 방호장치가 그 정도 변동에는 흔들림 없이 작동해야 한다는 뜻이다.</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
@@ -7496,7 +7532,7 @@
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 광전자식 방호장치&lt;/strong&gt;&lt;br&gt;산업안전보건법 제84조(안전인증), 「방호장치 안전인증 고시」. &lt;u&gt;±20 [%]&lt;/u&gt;라는 숫자가 갈림길이다. 광전자식은 &lt;u&gt;확동식 클러치 프레스에는 쓸 수 없다&lt;/u&gt;는 점도 함께 외운다. 한 번 물리면 멈출 수 없기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;±20 [%]&lt;/u&gt; — 100분의 10 이 아니다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C84%EC%A1%B0" target="_blank"&gt;제84조(안전인증)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 유해ㆍ위험기계등 중 근로자의 안전 및 보건에 위해(危害)를 미칠 수 있다고 인정되어 대통령령으로 정하는 것(이하 "안전인증대상기계등"이라 한다)을 제조하거나 수입하는 자(고용노동부령으로 정하는 안전인증대상기계등을 설치ㆍ이전하거나 주요 구조 부분을 변경하는 자를 포함한다. 이하 이 조 및 제85조부터 제87조까지의 규정에서 같다)는 안전인증대상기계등이 안전인증기준에 맞는지에 대하여 고용노동부장관이 실시하는 안전인증을 받아야 한다.&lt;br&gt;② 고용노동부장관은 다음 각 호의 어느 하나에 해당하는 경우에는 고용노동부령으로 정하는 바에 따라 제1항에 따른 안전인증의 전부 또는 일부를 면제할 수 있다.&lt;br&gt; 1. 연구ㆍ개발을 목적으로 제조ㆍ수입하거나 수출을 목적으로 제조하는 경우&lt;br&gt; 2. 고용노동부장관이 정하여 고시하는 외국의 안전인증기관에서 인증을 받은 경우&lt;br&gt; 3. 다른 법령에 따라 안전성에 관한 검사나 인증을 받은 경우로서 고용노동부령으로 정하는 경우&lt;br&gt;③ 안전인증대상기계등이 아닌 유해ㆍ위험기계등을 제조하거나 수입하는 자가 그 유해ㆍ위험기계등의 안전에 관한 성능 등을 평가받으려면 고용노동부장관에게 안전인증을 신청할 수 있다. 이 경우 고용노동부장관은 안전인증기준에 따라 안전인증을 할 수 있다.&lt;br&gt;④ 고용노동부장관은 제1항 및 제3항에 따른 안전인증(이하 "안전인증"이라 한다)을 받은 자가 안전인증기준을 지키고 있는지를 3년 이하의 범위에서 고용노동부령으로 정하는 주기마다 확인하여야 한다. 다만, 제2항에 따라 안전인증의 일부를 면제받은 경우에는 고용노동부령으로 정하는 바에 따라 확인의 전부 또는 일부를 생략할 수 있다.&lt;br&gt;▶ ⑤ 제1항에 따라 안전인증을 받은 자는 안전인증을 받은 안전인증대상기계등에 대하여 고용노동부령으로 정하는 바에 따라 제품명ㆍ모델명ㆍ제조수량ㆍ판매수량 및 판매처 현황 등의 사항을 기록하여 보존하여야 한다.&lt;br&gt;⑥ 고용노동부장관은 근로자의 안전 및 보건에 필요하다고 인정하는 경우 안전인증대상기계등을 제조ㆍ수입 또는 판매하는 자에게 고용노동부령으로 정하는 바에 따라 해당 안전인증대상기계등의 제조ㆍ수입 또는 판매에 관한 자료를 공단에 제출하게 할 수 있다.&lt;br&gt;⑦ 안전인증의 신청 방법ㆍ절차, 제4항에 따른 확인의 방법ㆍ절차, 그 밖에 필요한 사항은 고용노동부령으로 정한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 광전자식 방호장치&lt;/strong&gt;&lt;br&gt;산업안전보건법 제84조(안전인증), 「방호장치 안전인증 고시」. &lt;u&gt;±20 [%]&lt;/u&gt;라는 숫자가 갈림길이다. 광전자식은 &lt;u&gt;확동식 클러치 프레스에는 쓸 수 없다&lt;/u&gt;는 점도 함께 외운다. 한 번 물리면 멈출 수 없기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;±20 [%]&lt;/u&gt; — 100분의 10이 아니다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C84%EC%A1%B0" target="_blank"&gt;제84조(안전인증)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 유해ㆍ위험기계등 중 근로자의 안전 및 보건에 위해(危害)를 미칠 수 있다고 인정되어 대통령령으로 정하는 것(이하 "안전인증대상기계등"이라 한다)을 제조하거나 수입하는 자(고용노동부령으로 정하는 안전인증대상기계등을 설치ㆍ이전하거나 주요 구조 부분을 변경하는 자를 포함한다. 이하 이 조 및 제85조부터 제87조까지의 규정에서 같다)는 안전인증대상기계등이 안전인증기준에 맞는지에 대하여 고용노동부장관이 실시하는 안전인증을 받아야 한다.&lt;br&gt;② 고용노동부장관은 다음 각 호의 어느 하나에 해당하는 경우에는 고용노동부령으로 정하는 바에 따라 제1항에 따른 안전인증의 전부 또는 일부를 면제할 수 있다.&lt;br&gt; 1. 연구ㆍ개발을 목적으로 제조ㆍ수입하거나 수출을 목적으로 제조하는 경우&lt;br&gt; 2. 고용노동부장관이 정하여 고시하는 외국의 안전인증기관에서 인증을 받은 경우&lt;br&gt; 3. 다른 법령에 따라 안전성에 관한 검사나 인증을 받은 경우로서 고용노동부령으로 정하는 경우&lt;br&gt;③ 안전인증대상기계등이 아닌 유해ㆍ위험기계등을 제조하거나 수입하는 자가 그 유해ㆍ위험기계등의 안전에 관한 성능 등을 평가받으려면 고용노동부장관에게 안전인증을 신청할 수 있다. 이 경우 고용노동부장관은 안전인증기준에 따라 안전인증을 할 수 있다.&lt;br&gt;④ 고용노동부장관은 제1항 및 제3항에 따른 안전인증(이하 "안전인증"이라 한다)을 받은 자가 안전인증기준을 지키고 있는지를 3년 이하의 범위에서 고용노동부령으로 정하는 주기마다 확인하여야 한다. 다만, 제2항에 따라 안전인증의 일부를 면제받은 경우에는 고용노동부령으로 정하는 바에 따라 확인의 전부 또는 일부를 생략할 수 있다.&lt;br&gt;▶ ⑤ 제1항에 따라 안전인증을 받은 자는 안전인증을 받은 안전인증대상기계등에 대하여 고용노동부령으로 정하는 바에 따라 제품명ㆍ모델명ㆍ제조수량ㆍ판매수량 및 판매처 현황 등의 사항을 기록하여 보존하여야 한다.&lt;br&gt;⑥ 고용노동부장관은 근로자의 안전 및 보건에 필요하다고 인정하는 경우 안전인증대상기계등을 제조ㆍ수입 또는 판매하는 자에게 고용노동부령으로 정하는 바에 따라 해당 안전인증대상기계등의 제조ㆍ수입 또는 판매에 관한 자료를 공단에 제출하게 할 수 있다.&lt;br&gt;⑦ 안전인증의 신청 방법ㆍ절차, 제4항에 따른 확인의 방법ㆍ절차, 그 밖에 필요한 사항은 고용노동부령으로 정한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7875,7 @@
       </c>
       <c r="U53" s="32" t="inlineStr">
         <is>
-          <t>롤러의 급정지를 위한 방호장치를 설치하고자 한다. 앞면 롤러 직경이 36cm 이고, 분당회전속도가 50rpm이라면 급 정지거리는 약 얼마 이내이어야 하는가? (단, 무부하동작에 해당한다.)</t>
+          <t>롤러의 급정지를 위한 방호장치를 설치하고자 한다. 앞면 롤러 직경이 36cm이고, 분당회전속도가 50rpm이라면 급 정지거리는 약 얼마 이내이어야 하는가? (단, 무부하동작에 해당한다.)</t>
         </is>
       </c>
       <c r="V53" s="32" t="inlineStr"/>
@@ -7873,17 +7909,17 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>표면속도 $V = \dfrac{\pi D N}{1000} = \dfrac{\pi \times 360 \times 50}{1000} = 56.5$ [m/min] 로 30 이상이므로 &lt;strong&gt;원주의 1/2.5 이내&lt;/strong&gt;다. 원주는 $\pi \times 0.36 = 1.13$ [m] 이므로 $1.13 / 2.5 = 0.45$ [m] &lt;strong&gt;45 [cm]&lt;/strong&gt;다.</t>
+          <t>표면속도 $V = \dfrac{\pi D N}{1000} = \dfrac{\pi \times 360 \times 50}{1000} = 56.5$ [m/min]로 30 이상이므로 &lt;strong&gt;원주의 1/2.5 이내&lt;/strong&gt;다. 원주는 $\pi \times 0.36 = 1.13$ [m]이므로 $1.13 / 2.5 = 0.45$ [m] &lt;strong&gt;45 [cm]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>② 50 [cm] 는 원주를 크게 잡았을 때 나온다.&lt;br&gt;③ 55 [cm] 도 계산과 맞지 않는다.&lt;br&gt;④ 60 [cm] 는 1/2 로 나누었을 때에 가깝다.</t>
+          <t>② 50 [cm]는 원주를 크게 잡았을 때 나온다.&lt;br&gt;③ 55 [cm] 도 계산과 맞지 않는다.&lt;br&gt;④ 60 [cm]는 1/2로 나누었을 때에 가깝다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;표면속도가 &lt;strong&gt;30 [m/min] 미만이면 원주의 1/3 이내&lt;/strong&gt;, &lt;strong&gt;30 이상이면 1/2.5 이내&lt;/strong&gt;다. $V$ 를 구할 때 지름의 단위를 [mm] 로 맞추는 것이 실수하기 쉬운 대목이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;빠를수록 더 짧게 멈춰야 한다&lt;/u&gt; — 30 미만 1/3, 30 이상 1/2.5.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;표면속도가 &lt;strong&gt;30 [m/min] 미만이면 원주의 1/3 이내&lt;/strong&gt;, &lt;strong&gt;30 이상이면 1/2.5 이내&lt;/strong&gt;다. $V$를 구할 때 지름의 단위를 [mm]로 맞추는 것이 실수하기 쉬운 대목이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;빠를수록 더 짧게 멈춰야 한다&lt;/u&gt; — 30 미만 1/3, 30 이상 1/2.5.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8613,14 +8649,14 @@
       </c>
       <c r="U59" s="32" t="inlineStr">
         <is>
-          <t>다음 중 지게차의 작업 상태별 안정도에 관한 설명으로 틀 린 것은? (단, V는 최고속도(km/h) 이다.)</t>
+          <t>다음 중 지게차의 작업 상태별 안정도에 관한 설명으로 틀 린 것은? (단, V는 최고속도(km/h)이다.)</t>
         </is>
       </c>
       <c r="V59" s="32" t="inlineStr"/>
       <c r="W59" s="32" t="inlineStr"/>
       <c r="X59" s="32" t="inlineStr">
         <is>
-          <t>기준 부하상태의 하역작업 시의 전후 안정도는 20% 이 내이다.</t>
+          <t>기준 부하상태의 하역작업 시의 전후 안정도는 20%이 내이다.</t>
         </is>
       </c>
       <c r="Y59" s="32" t="inlineStr"/>
@@ -8632,7 +8668,7 @@
       <c r="AA59" s="32" t="inlineStr"/>
       <c r="AB59" s="32" t="inlineStr">
         <is>
-          <t>기준 무부하상태에서 주행 시의 전후 안정도는 18% 이 내이다.</t>
+          <t>기준 무부하상태에서 주행 시의 전후 안정도는 18%이 내이다.</t>
         </is>
       </c>
       <c r="AC59" s="32" t="inlineStr"/>
@@ -8647,7 +8683,7 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>하역작업 시 &lt;strong&gt;전후 안정도는 4 [%] 이내&lt;/strong&gt;(5톤 이상은 3.5 [%])다. 20 [%] 가 아니다. 짐을 들어 올린 상태는 무게중심이 높아 조금만 기울어도 넘어가므로 &lt;strong&gt;가장 엄격한&lt;/strong&gt; 기준이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;하역작업 시 (기준 부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt; (5톤 이상은 3.5 [%])&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;하역작업 시 (기준 부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좌우&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;주행 시 (기준 무부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;주행 시 (기준 무부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좌우&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
+          <t>하역작업 시 &lt;strong&gt;전후 안정도는 4 [%] 이내&lt;/strong&gt;(5톤 이상은 3.5 [%])다. 20 [%]가 아니다. 짐을 들어 올린 상태는 무게중심이 높아 조금만 기울어도 넘어가므로 &lt;strong&gt;가장 엄격한&lt;/strong&gt; 기준이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;하역작업 시 (기준 부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt; (5톤 이상은 3.5 [%])&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;하역작업 시 (기준 부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좌우&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;주행 시 (기준 무부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;주행 시 (기준 무부하)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좌우&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
@@ -8776,12 +8812,12 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>$T = \dfrac{W}{2 \cos ( \theta / 2 )}$ 이므로 $T = 3 / ( 2 \times \cos 27.5 ^{\circ} ) = 3 / ( 2 \times 0.8870 ) = 1.69$, 곧 &lt;strong&gt;약 1.7 [kN]&lt;/strong&gt;이다.&lt;img src="safe_A_2026_01_058_exp1.png"&gt;&lt;em&gt;줄걸이 각도와 장력 — 벌어질수록 로프에 걸리는 힘이 커진다&lt;/em&gt;</t>
+          <t>$T = \dfrac{W}{2 \cos ( \theta / 2 )}$이므로 $T = 3 / ( 2 \times \cos 27.5 ^{\circ} ) = 3 / ( 2 \times 0.8870 ) = 1.69$, 곧 &lt;strong&gt;약 1.7 [kN]&lt;/strong&gt;이다.&lt;img src="safe_A_2026_01_058_exp1.png"&gt;&lt;em&gt;줄걸이 각도와 장력 — 벌어질수록 로프에 걸리는 힘이 커진다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 1.3 은 각도를 무시하고 절반으로 나눈 값보다도 작아 성립하지 않는다.&lt;br&gt;③ 2.0 은 각도를 90° 안팎으로 잡았을 때 나오는 값이다.&lt;br&gt;④ 2.3 은 각도를 120° 가까이 잡았을 때 나오는 값이다.</t>
+          <t>① 1.3은 각도를 무시하고 절반으로 나눈 값보다도 작아 성립하지 않는다.&lt;br&gt;③ 2.0은 각도를 90° 안팎으로 잡았을 때 나오는 값이다.&lt;br&gt;④ 2.3은 각도를 120° 가까이 잡았을 때 나오는 값이다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
@@ -9034,17 +9070,17 @@
       </c>
       <c r="AG62" s="32" t="inlineStr">
         <is>
-          <t>원주속도 &lt;strong&gt;30 [m/min] 이상이면 원주의 1/2.5 이내&lt;/strong&gt;에 멈춰야 한다. $6 / 2.5 = 2.4$ [m] 이므로 &lt;strong&gt;2.4 [m] 이내&lt;/strong&gt; 여야 하는데 2.6 [m] 는 이를 넘는다.</t>
+          <t>원주속도 &lt;strong&gt;30 [m/min] 이상이면 원주의 1/2.5 이내&lt;/strong&gt;에 멈춰야 한다. $6 / 2.5 = 2.4$ [m]이므로 &lt;strong&gt;2.4 [m] 이내&lt;/strong&gt; 여야 하는데 2.6 [m]는 이를 넘는다.</t>
         </is>
       </c>
       <c r="AH62" s="32" t="inlineStr">
         <is>
-          <t>① 25 [m/min] 는 30 미만이므로 1/3 기준이다. $5 / 3 = 1.67$ [m] 이내이므로 1.6 [m] 는 적합하다.&lt;br&gt;② 35 [m/min] 는 30 이상이므로 1/2.5 기준이다. $7 / 2.5 = 2.8$ [m] 이내이므로 적합하다.&lt;br&gt;④ 20 [m/min] 는 30 미만이므로 1/3 기준이다. $8 / 3 = 2.67$ [m] 이내이므로 2.6 [m] 는 적합하다.</t>
+          <t>① 25 [m/min]는 30 미만이므로 1/3 기준이다. $5 / 3 = 1.67$ [m] 이내이므로 1.6 [m]는 적합하다.&lt;br&gt;② 35 [m/min]는 30 이상이므로 1/2.5 기준이다. $7 / 2.5 = 2.8$ [m] 이내이므로 적합하다.&lt;br&gt;④ 20 [m/min]는 30 미만이므로 1/3 기준이다. $8 / 3 = 2.67$ [m] 이내이므로 2.6 [m]는 적합하다.</t>
         </is>
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;안전보건규칙 제147조(급정지장치의 성능). &lt;u&gt;30 [m/min] 미만은 원주의 1/3 이내, 30 [m/min] 이상은 1/2.5 이내&lt;/u&gt;. &lt;u&gt;빠를수록 더 엄격&lt;/u&gt; 한 것은, 그만큼 손이 빨리 딸려 들어가기 때문이다. 급정지장치의 조작부는 &lt;u&gt;손 조작식 밑면에서 1.8 [m] 이내 · 복부 조작식 0.8~1.1 [m] · 무릎 조작식 0.6 [m] 이내&lt;/u&gt;에 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만 1/3, 이상 1/2.5&lt;/u&gt; — 빠를수록 엄격.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C147%EC%A1%B0" target="_blank"&gt;제147조(설계기준 준수)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제147조(설계기준 준수) 사업주는 이동식 크레인을 사용하는 경우에 그 이동식 크레인이 넘어지거나 그 이동식 크레인의 구조 부분을 구성하는 강재 등이 변형되거나 부러지는 일 등을 방지하기 위하여 해당 이동식 크레인의 설계기준(제조자가 제공하는 사용설명서)을 준수하여야 한다. &amp;lt;개정 2024.6.28&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;안전보건규칙 제147조(급정지장치의 성능). &lt;u&gt;30 [m/min] 미만은 원주의 1/3 이내, 30 [m/min] 이상은 1/2.5 이내&lt;/u&gt;. &lt;u&gt;빠를수록 더 엄격&lt;/u&gt;한 것은, 그만큼 손이 빨리 딸려 들어가기 때문이다. 급정지장치의 조작부는 &lt;u&gt;손 조작식 밑면에서 1.8 [m] 이내 · 복부 조작식 0.8~1.1 [m] · 무릎 조작식 0.6 [m] 이내&lt;/u&gt;에 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만 1/3, 이상 1/2.5&lt;/u&gt; — 빠를수록 엄격.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C147%EC%A1%B0" target="_blank"&gt;제147조(설계기준 준수)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제147조(설계기준 준수) 사업주는 이동식 크레인을 사용하는 경우에 그 이동식 크레인이 넘어지거나 그 이동식 크레인의 구조 부분을 구성하는 강재 등이 변형되거나 부러지는 일 등을 방지하기 위하여 해당 이동식 크레인의 설계기준(제조자가 제공하는 사용설명서)을 준수하여야 한다. &amp;lt;개정 2024.6.28&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9163,17 +9199,17 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>저항이 모두 &lt;strong&gt;직렬&lt;/strong&gt;로 이어진다. $R = 10 + 1 + 20 = 31$ [kΩ] 이므로 $I = 90 / 31 {,} 000 = 0.0029$ [A], 곧 &lt;strong&gt;약 2.90 [mA]&lt;/strong&gt;다.&lt;img src="safe_A_2026_01_061_exp1.png"&gt;&lt;em&gt;감전 경로의 등가회로 — 저항은 모두 직렬로 더한다&lt;/em&gt;</t>
+          <t>저항이 모두 &lt;strong&gt;직렬&lt;/strong&gt;로 이어진다. $R = 10 + 1 + 20 = 31$ [kΩ]이므로 $I = 90 / 31 {,} 000 = 0.0029$ [A], 곧 &lt;strong&gt;약 2.90 [mA]&lt;/strong&gt;다.&lt;img src="safe_A_2026_01_061_exp1.png"&gt;&lt;em&gt;감전 경로의 등가회로 — 저항은 모두 직렬로 더한다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 0.19 [mA] 는 저항을 열 배로 잡았을 때 나오는 값이다.&lt;br&gt;② 0.29 [mA] 도 자릿수가 한 자리 어긋난 값이다.&lt;br&gt;③ 1.96 [mA] 는 접촉저항 하나를 빠뜨렸을 때 나오는 값에 가깝다.</t>
+          <t>① 0.19 [mA]는 저항을 열 배로 잡았을 때 나오는 값이다.&lt;br&gt;② 0.29 [mA] 도 자릿수가 한 자리 어긋난 값이다.&lt;br&gt;③ 1.96 [mA]는 접촉저항 하나를 빠뜨렸을 때 나오는 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전 경로의 등가회로&lt;/strong&gt;&lt;br&gt;전류는 &lt;u&gt;손 접촉저항 → 인체 내부저항 → 발과 대지의 접촉저항&lt;/u&gt;을 차례로 지나므로 모두 더한다. 교류 아크용접기의 무부하 전압이 70~80 [V] 로 높은 것이 위험의 뿌리이며, 그래서 &lt;u&gt;자동전격방지장치&lt;/u&gt;로 아크가 꺼지면 25 [V] 이하로 낮춘다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 저항은 &lt;u&gt;모두 직렬로 더한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전 경로의 등가회로&lt;/strong&gt;&lt;br&gt;전류는 &lt;u&gt;손 접촉저항 → 인체 내부저항 → 발과 대지의 접촉저항&lt;/u&gt;을 차례로 지나므로 모두 더한다. 교류 아크용접기의 무부하 전압이 70~80 [V]로 높은 것이 위험의 뿌리이며, 그래서 &lt;u&gt;자동전격방지장치&lt;/u&gt;로 아크가 꺼지면 25 [V] 이하로 낮춘다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 저항은 &lt;u&gt;모두 직렬로 더한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9328,12 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;50 [V] 를 초과&lt;/strong&gt; 하는 저압 기계기구로서 사람이 쉽게 접촉할 우려가 있는 곳에 시설하는 것에는 누전차단기를 설치한다. 50 [V] 는 국제적으로 &lt;strong&gt;교류에서 사람이 견딜 수 있다고 보는 한계&lt;/strong&gt;로 삼는 값이다.</t>
+          <t>&lt;strong&gt;50 [V]를 초과&lt;/strong&gt;하는 저압 기계기구로서 사람이 쉽게 접촉할 우려가 있는 곳에 시설하는 것에는 누전차단기를 설치한다. 50 [V]는 국제적으로 &lt;strong&gt;교류에서 사람이 견딜 수 있다고 보는 한계&lt;/strong&gt;로 삼는 값이다.</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 30 [V] 는 우리나라에서 흔히 말하는 「안전전압」이지 누전차단기 시설 기준은 아니다.&lt;br&gt;② 40 [V] 라는 기준은 없다.&lt;br&gt;④ 60 [V] 는 직류 쪽에서 쓰이는 값이다.</t>
+          <t>① 30 [V]는 우리나라에서 흔히 말하는 「안전전압」이지 누전차단기 시설 기준은 아니다.&lt;br&gt;② 40 [V]라는 기준은 없다.&lt;br&gt;④ 60 [V]는 직류 쪽에서 쓰이는 값이다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9426,7 +9462,7 @@
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>① 철판·철골 위 등 도전성이 높은 장소의 이동형 기기는 설치 대상이다.&lt;br&gt;② 대지전압 150 [V] 를 초과하는 휴대형 기기는 설치 대상이다. 220 [V] 는 이를 넘는다.&lt;br&gt;③ 임시배선 전로가 설치된 장소의 이동형 기기도 설치 대상이다.</t>
+          <t>① 철판·철골 위 등 도전성이 높은 장소의 이동형 기기는 설치 대상이다.&lt;br&gt;② 대지전압 150 [V]를 초과하는 휴대형 기기는 설치 대상이다. 220 [V]는 이를 넘는다.&lt;br&gt;③ 임시배선 전로가 설치된 장소의 이동형 기기도 설치 대상이다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
@@ -9516,7 +9552,7 @@
       </c>
       <c r="U66" s="32" t="inlineStr">
         <is>
-          <t>인체의 전기저항을 0.5kΩ이라고 하면 심실세동을 일으키는 위험한계 에너지는 몇 J 인가? (단, 심실세동전류값 1초로 한다.)</t>
+          <t>인체의 전기저항을 0.5kΩ이라고 하면 심실세동을 일으키는 위험한계 에너지는 몇 J 인가? (단, 심실세동전류값 I = 165 / √T [mA]의 Dalziel의 식을 이용하며, 통전시간은 1초로 한다.)</t>
         </is>
       </c>
       <c r="V66" s="32" t="inlineStr"/>
@@ -9535,7 +9571,7 @@
       <c r="AA66" s="32" t="inlineStr"/>
       <c r="AB66" s="32" t="inlineStr">
         <is>
-          <t>11.6 mA 의 Dalziel의 식을 이용하며, 통전시간은</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AC66" s="32" t="inlineStr"/>
@@ -9550,17 +9586,17 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T$ 이다. $I = 165 / \sqrt{1} = 165$ [mA] $= 0.165$ [A] 이므로 $W = ( 0.165 )^{2} \times 500 \times 1 = 0.027225 \times 500 = 13.6$ [J] 다.</t>
+          <t>$W = I^{2} R T$이다. $I = 165 / \sqrt{1} = 165$ [mA] $= 0.165$ [A]이므로 $W = ( 0.165 )^{2} \times 500 \times 1 = 0.027225 \times 500 = 13.6$ [J]다.</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>② 12.6 은 전류를 제곱하지 않았을 때 나오는 값이다.&lt;br&gt;③ 11.6 은 저항을 잘못 잡았을 때 나오는 값이다.&lt;br&gt;④ 10.6 은 통전시간을 달리 잡았을 때 나오는 값이다.</t>
+          <t>② 12.6은 전류를 제곱하지 않았을 때 나오는 값이다.&lt;br&gt;③ 11.6은 저항을 잘못 잡았을 때 나오는 값이다.&lt;br&gt;④ 10.6은 통전시간을 달리 잡았을 때 나오는 값이다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Dalziel 의 심실세동 전류식&lt;/strong&gt;&lt;br&gt;$I = 165 / \sqrt{T}$ [mA] (체중 70 [kg] 기준, 통전시간 T 는 초). 위험한계 에너지는 $W = I^{2} R T$ 로 구하며 대략 &lt;u&gt;13.6 [J]&lt;/u&gt;이 나온다. 통전시간이 &lt;u&gt;4배가 되면 위험전류는 절반&lt;/u&gt;이 되므로, 누전차단기의 동작시간을 짧게 하는 것이 결정적이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = 165 / \sqrt{T}$ [mA], $W = I^{2} R T$. &lt;u&gt;1초에 13.6 [J]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항에서는 「$I = 165 / \sqrt{T}$ [mA] 의 Dalziel 식을 이용하며」라는 단서가 지문에 있었으나, 조판 과정에서 선택지 쪽으로 밀려 들어가 있었다. 이 책에서는 지문으로 되돌려 실었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Dalziel의 심실세동 전류식&lt;/strong&gt;&lt;br&gt;$I = 165 / \sqrt{T}$ [mA] (체중 70 [kg] 기준, 통전시간 T는 초). 위험한계 에너지는 $W = I^{2} R T$로 구하며 대략 &lt;u&gt;13.6 [J]&lt;/u&gt;이 나온다. 통전시간이 &lt;u&gt;4배가 되면 위험전류는 절반&lt;/u&gt;이 되므로, 누전차단기의 동작시간을 짧게 하는 것이 결정적이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = 165 / \sqrt{T}$ [mA], $W = I^{2} R T$. &lt;u&gt;1초에 13.6 [J]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항에서는 「$I = 165 / \sqrt{T}$ [mA]의 Dalziel 식을 이용하며」라는 단서가 지문에 있었으나, 조판 과정에서 선택지 쪽으로 밀려 들어가 있었다. 이 책에서는 지문으로 되돌려 실었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9854,7 @@
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전격사의 세 가지 기전&lt;/strong&gt;&lt;br&gt;전격사의 3대 기전. &lt;u&gt;심실세동(혈액순환 정지) · 호흡중추 마비(호흡 정지) · 흉부 수축에 의한 질식&lt;/u&gt;. 셋 다 &lt;u&gt;전류가 몸을 지나며 신경과 근육을 교란&lt;/u&gt; 해서 생긴다. 그래서 응급조치의 핵심이 &lt;u&gt;심폐소생술&lt;/u&gt;이다.</t>
+          <t>&lt;strong&gt;전격사의 세 가지 기전&lt;/strong&gt;&lt;br&gt;전격사의 3대 기전. &lt;u&gt;심실세동(혈액순환 정지) · 호흡중추 마비(호흡 정지) · 흉부 수축에 의한 질식&lt;/u&gt;. 셋 다 &lt;u&gt;전류가 몸을 지나며 신경과 근육을 교란&lt;/u&gt;해서 생긴다. 그래서 응급조치의 핵심이 &lt;u&gt;심폐소생술&lt;/u&gt;이다.</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9978,7 @@
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>② 앞자리가 2이면 지름 &lt;strong&gt;12.5 [mm] 이상&lt;/strong&gt;이다. 10 [mm] 가 아니다.&lt;br&gt;③ 제2 특성 숫자는 &lt;strong&gt;물&lt;/strong&gt;에 대한 보호이지 분진이 아니다.&lt;br&gt;④ 제2 특성 숫자는 물에 대한 보호다.</t>
+          <t>② 앞자리가 2이면 지름 &lt;strong&gt;12.5 [mm] 이상&lt;/strong&gt;이다. 10 [mm]가 아니다.&lt;br&gt;③ 제2 특성 숫자는 &lt;strong&gt;물&lt;/strong&gt;에 대한 보호이지 분진이 아니다.&lt;br&gt;④ 제2 특성 숫자는 물에 대한 보호다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
@@ -10027,7 +10063,11 @@
           <t>다음 빈칸에 들어갈 내용으로 알맞은 것은?</t>
         </is>
       </c>
-      <c r="V70" s="32" t="inlineStr"/>
+      <c r="V70" s="32" t="inlineStr">
+        <is>
+          <t>「교류 특고압 가공전선로에서 발생하는 극저주파 전자계는 지표상 1m에서 전계가 ( ⓐ ), 자계가 ( ⓑ )가 되도록 시설하는 등 상시 정전유도 및 전자유도 작용에 의하여 사람에게 위험을 줄 우려가 없도록 시설하여야 한다.」</t>
+        </is>
+      </c>
       <c r="W70" s="32" t="inlineStr"/>
       <c r="X70" s="32" t="inlineStr">
         <is>
@@ -10063,12 +10103,12 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 전계와 자계 모두 자릿수가 한 단계씩 작다.&lt;br&gt;② 자계 8.33 [μT] 는 자릿수가 한 단계 작다.&lt;br&gt;④ 전계 35 [kV/m] 와 자계 833 [μT] 는 한 단계씩 크다.</t>
+          <t>① 전계와 자계 모두 자릿수가 한 단계씩 작다.&lt;br&gt;② 자계 8.33 [μT]는 자릿수가 한 단계 작다.&lt;br&gt;④ 전계 35 [kV/m]와 자계 833 [μT]는 한 단계씩 크다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전기설비기술기준 — 전자파 인체보호기준&lt;/strong&gt;&lt;br&gt;국제비이온화방사보호위원회(ICNIRP) 권고를 받아들인 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3.5 와 83.3&lt;/u&gt;을 한 묶음으로.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전기설비기술기준 — 전자파 인체보호기준&lt;/strong&gt;&lt;br&gt;국제비이온화방사보호위원회(ICNIRP) 권고를 받아들인 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3.5와 83.3&lt;/u&gt;을 한 묶음으로.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10316,17 +10356,17 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>EPL 의 뒤 글자는 보호 수준을 나타내며 &lt;strong&gt;a(매우 높음) · b(높음) · c(강화된)&lt;/strong&gt; 세 가지다. 다만 &lt;strong&gt;광산용 M 은 Ma 와 Mb 두 가지뿐&lt;/strong&gt;이라 &lt;strong&gt;Mc 는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;기기보호등급(EPL)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조합&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;G — 가스&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Ga · Gb · Gc&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Ga 는 0종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;D — 분진&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Da · Db · Dc&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Da 는 20종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;M — 광산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Ma · Mb&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Mc 는 없다&lt;/u&gt; — 갈림길&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>EPL의 뒤 글자는 보호 수준을 나타내며 &lt;strong&gt;a(매우 높음) · b(높음) · c(강화된)&lt;/strong&gt; 세 가지다. 다만 &lt;strong&gt;광산용 M은 Ma와 Mb 두 가지뿐&lt;/strong&gt;이라 &lt;strong&gt;Mc는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;기기보호등급(EPL)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조합&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;G — 가스&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Ga · Gb · Gc&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Ga는 0종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;D — 분진&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Da · Db · Dc&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;Da는 20종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;M — 광산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Ma · Mb&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Mc는 없다&lt;/u&gt; — 갈림길&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>① EPL Ga 는 가스 분위기용 최고 등급이다.&lt;br&gt;② EPL Ma 는 광산용 최고 등급이다.&lt;br&gt;③ EPL Dc 는 분진 분위기용 c 등급이다.</t>
+          <t>① EPL Ga는 가스 분위기용 최고 등급이다.&lt;br&gt;② EPL Ma는 광산용 최고 등급이다.&lt;br&gt;③ EPL Dc는 분진 분위기용 c 등급이다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기기보호등급(EPL)&lt;/strong&gt;&lt;br&gt;EPL(Equipment Protection Level). 앞 글자는 대상 분위기 — &lt;u&gt;G(gas) · D(dust) · M(mine)&lt;/u&gt;. 뒤 글자는 보호 수준 — &lt;u&gt;a · b · c&lt;/u&gt;. 조합은 &lt;u&gt;Ga/Gb/Gc · Da/Db/Dc · Ma/Mb&lt;/u&gt;로 여덟 가지이며, &lt;u&gt;M 에만 c 가 없다&lt;/u&gt;는 것이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;M 에만 c 가 없다&lt;/u&gt; — Ma·Mb 뿐.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기기보호등급(EPL)&lt;/strong&gt;&lt;br&gt;EPL(Equipment Protection Level). 앞 글자는 대상 분위기 — &lt;u&gt;G(gas) · D(dust) · M(mine)&lt;/u&gt;. 뒤 글자는 보호 수준 — &lt;u&gt;a · b · c&lt;/u&gt;. 조합은 &lt;u&gt;Ga/Gb/Gc · Da/Db/Dc · Ma/Mb&lt;/u&gt;로 여덟 가지이며, &lt;u&gt;M 에만 c가 없다&lt;/u&gt;는 것이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;M 에만 c가 없다&lt;/u&gt; — Ma·Mb뿐.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10495,7 @@
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압 방폭구조(d)의 세 조건&lt;/strong&gt;&lt;br&gt;화염이 좁은 틈을 지나며 식어 밖에 불을 옮기지 못하는 원리다. 그 틈의 한계값이 &lt;strong&gt;최대안전틈새(MESG)&lt;/strong&gt;이며, 폭발등급 ⅡA·ⅡB·ⅡC 를 가르는 기준이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;① 압력에 견딜 것 ② 화염이 새 나가지 않을 것 ③ 표면온도가 낮을 것&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압 방폭구조(d)의 세 조건&lt;/strong&gt;&lt;br&gt;화염이 좁은 틈을 지나며 식어 밖에 불을 옮기지 못하는 원리다. 그 틈의 한계값이 &lt;strong&gt;최대안전틈새(MESG)&lt;/strong&gt;이며, 폭발등급 ⅡA·ⅡB·ⅡC를 가르는 기준이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;① 압력에 견딜 것 ② 화염이 새 나가지 않을 것 ③ 표면온도가 낮을 것&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10580,7 @@
       </c>
       <c r="U74" s="32" t="inlineStr">
         <is>
-          <t>교류 아크용접기의 허용사용률(%)은? (단, 정격사용률은 10%, 2차 정격전류는 500A, 교류 아크용접기의 사용전류는 250A 이다.)</t>
+          <t>교류 아크용접기의 허용사용률(%)은? (단, 정격사용률은 10%, 2차 정격전류는 500A, 교류 아크용접기의 사용전류는 250A이다.)</t>
         </is>
       </c>
       <c r="V74" s="32" t="inlineStr"/>
@@ -10574,12 +10614,12 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$\text{허용사용률} = ( \dfrac{\text{정격} 2 \text{차 전류}}{\text{실제 사용전류}} )^{2} \times \text{정격사용률}$ 이므로 $( 500 / 250 )^{2} \times 10 = 40$ [%] 다.</t>
+          <t>$\text{허용사용률} = ( \dfrac{\text{정격} 2 \text{차 전류}}{\text{실제 사용전류}} )^{2} \times \text{정격사용률}$이므로 $( 500 / 250 )^{2} \times 10 = 40$ [%]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 30 [%] 는 전류비를 제곱하지 않았을 때에 가까운 값이다.&lt;br&gt;③ 50 [%] 는 계산과 맞지 않는다.&lt;br&gt;④ 60 [%] 도 계산과 맞지 않는다.</t>
+          <t>① 30 [%]는 전류비를 제곱하지 않았을 때에 가까운 값이다.&lt;br&gt;③ 50 [%]는 계산과 맞지 않는다.&lt;br&gt;④ 60 [%] 도 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
@@ -10817,7 +10857,7 @@
       <c r="AA76" s="32" t="inlineStr"/>
       <c r="AB76" s="32" t="inlineStr">
         <is>
-          <t>유자격자가 아닌 근로자가 근로자의 몸 또는 긴 도전성 물체가 방호되지 않은 충전전로에서 대지전압이 50kV 이 하인 경우에는 400cm 이내로 접근할 수 없도록 하여야 한다.</t>
+          <t>유자격자가 아닌 근로자가 근로자의 몸 또는 긴 도전성 물체가 방호되지 않은 충전전로에서 대지전압이 50kV이 하인 경우에는 400cm 이내로 접근할 수 없도록 하여야 한다.</t>
         </is>
       </c>
       <c r="AC76" s="32" t="inlineStr"/>
@@ -10832,7 +10872,7 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>대지전압 50 [kV] 이하이면 &lt;strong&gt;300 [cm] 이내&lt;/strong&gt;로 접근하지 못하게 한다. 400 [cm] 가 아니다. 50 [kV] 를 넘으면 &lt;strong&gt;10 [kV] 마다 10 [cm] 씩&lt;/strong&gt; 거리를 늘린다.</t>
+          <t>대지전압 50 [kV] 이하이면 &lt;strong&gt;300 [cm] 이내&lt;/strong&gt;로 접근하지 못하게 한다. 400 [cm]가 아니다. 50 [kV]를 넘으면 &lt;strong&gt;10 [kV] 마다 10 [cm] 씩&lt;/strong&gt; 거리를 늘린다.</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
@@ -11219,7 +11259,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>방향이 거꾸로다. 유속이 빠를수록 &lt;strong&gt;유동대전&lt;/strong&gt;이 심해지므로 &lt;strong&gt;유속을 제한&lt;/strong&gt; 해야 한다. 특히 이황화탄소는 최소발화에너지가 매우 작아(약 0.009 [mJ]) 아주 작은 방전에도 불이 붙으므로 &lt;strong&gt;1 [m/s] 이하&lt;/strong&gt;로 더 엄격하게 묶는다.</t>
+          <t>방향이 거꾸로다. 유속이 빠를수록 &lt;strong&gt;유동대전&lt;/strong&gt;이 심해지므로 &lt;strong&gt;유속을 제한&lt;/strong&gt;해야 한다. 특히 이황화탄소는 최소발화에너지가 매우 작아(약 0.009 [mJ]) 아주 작은 방전에도 불이 붙으므로 &lt;strong&gt;1 [m/s] 이하&lt;/strong&gt;로 더 엄격하게 묶는다.</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11817,7 +11857,11 @@
           <t>산업안전보건법령상 다음 인화성 가스의 정의에서 ( ) 안에 알맞은 값은?</t>
         </is>
       </c>
-      <c r="V84" s="32" t="inlineStr"/>
+      <c r="V84" s="32" t="inlineStr">
+        <is>
+          <t>「인화성 가스」란 인화한계 농도의 최저한도가 ( ㉠ )% 이하 또는 최고한도와 최저한도의 차가 ( ㉡ )% 이상인 것으로서 표준압력(101.3 kPa), 20℃에서 가스 상태인 물질을 말한다.</t>
+        </is>
+      </c>
       <c r="W84" s="32" t="inlineStr"/>
       <c r="X84" s="32" t="inlineStr">
         <is>
@@ -11848,17 +11892,17 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하한이 13 [%] 이하이거나 상하한의 차가 12 [%] 이상&lt;/strong&gt;인 가스를 인화성 가스로 본다. 「&lt;strong&gt;13 과 12&lt;/strong&gt;」를 묶어 외운다.</t>
+          <t>&lt;strong&gt;하한이 13 [%] 이하이거나 상하한의 차가 12 [%] 이상&lt;/strong&gt;인 가스를 인화성 가스로 본다. 「&lt;strong&gt;13과 12&lt;/strong&gt;」를 묶어 외운다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>② 상하한의 차가 15 [%] 가 아니라 12 [%] 다.&lt;br&gt;③ 하한이 12 [%] 가 아니라 13 [%] 다.&lt;br&gt;④ 둘 다 어긋난다.</t>
+          <t>② 상하한의 차가 15 [%]가 아니라 12 [%]다.&lt;br&gt;③ 하한이 12 [%]가 아니라 13 [%]다.&lt;br&gt;④ 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표1 — 인화성 가스의 정의&lt;/strong&gt;&lt;br&gt;안전보건규칙 별표1(위험물질의 종류) 제3호 인화성 가스. 두 조건 중 &lt;u&gt;하나만 만족해도&lt;/u&gt; 인화성 가스다. 「하한이 낮아서 위험하거나, 범위가 넓어서 위험하거나」 둘 중 하나면 규제 대상으로 삼는다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;13 과 12&lt;/u&gt; — 하한 13 [%] 이하 또는 상하한 차 12 [%] 이상.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 1&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표1 — 인화성 가스의 정의&lt;/strong&gt;&lt;br&gt;안전보건규칙 별표1(위험물질의 종류) 제3호 인화성 가스. 두 조건 중 &lt;u&gt;하나만 만족해도&lt;/u&gt; 인화성 가스다. 「하한이 낮아서 위험하거나, 범위가 넓어서 위험하거나」 둘 중 하나면 규제 대상으로 삼는다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;13과 12&lt;/u&gt; — 하한 13 [%] 이하 또는 상하한 차 12 [%] 이상.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 1&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -11977,12 +12021,12 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 이므로, 하한이 높은 &lt;strong&gt;메탄이 적게 섞일수록&lt;/strong&gt; 혼합가스의 하한이 낮아진다. 메탄 20 [%] 인 ①이 가장 낮다. $100 / L = 20 / 5 + 30 / 2 + 50 / 2.1 = 42.81$ 이므로 $L = 2.34$ [%] 다.</t>
+          <t>$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$이므로, 하한이 높은 &lt;strong&gt;메탄이 적게 섞일수록&lt;/strong&gt; 혼합가스의 하한이 낮아진다. 메탄 20 [%] 인 ①이 가장 낮다. $100 / L = 20 / 5 + 30 / 2 + 50 / 2.1 = 42.81$이므로 $L = 2.34$ [%]다.</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>② 메탄이 30 [%] 로 늘어 하한이 ①보다 높아진다.&lt;br&gt;③ 메탄이 40 [%] 로 더 늘어 하한이 더 높아진다.&lt;br&gt;④ 메탄이 50 [%] 로 가장 많아 하한이 가장 높다.</t>
+          <t>② 메탄이 30 [%]로 늘어 하한이 ①보다 높아진다.&lt;br&gt;③ 메탄이 40 [%]로 더 늘어 하한이 더 높아진다.&lt;br&gt;④ 메탄이 50 [%]로 가장 많아 하한이 가장 높다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
@@ -12075,7 +12119,11 @@
           <t>다음 표의 가스(A~D)를 위험도가 큰 것부터 작은 순으로 나열한 것은?</t>
         </is>
       </c>
-      <c r="V86" s="32" t="inlineStr"/>
+      <c r="V86" s="32" t="inlineStr">
+        <is>
+          <t>A : 폭발하한값 4.0 [vol%] · 폭발상한값 75.0 [vol%]&lt;br&gt;B : 폭발하한값 3.0 [vol%] · 폭발상한값 80.0 [vol%]&lt;br&gt;C : 폭발하한값 1.25 [vol%] · 폭발상한값 44.0 [vol%]&lt;br&gt;D : 폭발하한값 2.5 [vol%] · 폭발상한값 81.0 [vol%]</t>
+        </is>
+      </c>
       <c r="W86" s="32" t="inlineStr"/>
       <c r="X86" s="32" t="inlineStr">
         <is>
@@ -12106,7 +12154,7 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>위험도는 $H = \dfrac{U - L}{L}$ 로 구한다. &lt;strong&gt;상한과 하한의 차가 클수록, 하한이 낮을수록&lt;/strong&gt; 위험도가 크다. 표의 값을 각각 대입해 큰 것부터 늘어놓으면 C – D – B – A 순이 된다.</t>
+          <t>위험도는 $H = \dfrac{U - L}{L}$로 구한다. &lt;strong&gt;상한과 하한의 차가 클수록, 하한이 낮을수록&lt;/strong&gt; 위험도가 크다. 표의 값을 각각 대입해 큰 것부터 늘어놓으면 C – D – B – A 순이 된다.</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
@@ -12116,7 +12164,7 @@
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가스의 위험도&lt;/strong&gt;&lt;br&gt;위험도 $H = ( U - L ) / L$. 대표값 — &lt;u&gt;아세틸렌 2.5~81 [%] 이므로 H = 31.4&lt;/u&gt;로 압도적으로 크고, &lt;u&gt;수소 4~75 [%] 이면 H = 17.75&lt;/u&gt;, &lt;u&gt;메탄 5~15 [%] 이면 H = 2&lt;/u&gt;다. &lt;u&gt;분모가 하한&lt;/u&gt;이라는 점 때문에 하한이 낮은 가스가 크게 유리해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$ — &lt;u&gt;분모가 하한&lt;/u&gt;이라 하한이 낮을수록 크다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 가스별 폭발범위 표는 이 책에 옮기지 못했다. 이 유형은 &lt;u&gt;식에 대입해 큰 것부터 늘어놓는&lt;/u&gt; 절차만 익히면 표가 달라져도 풀린다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가스의 위험도&lt;/strong&gt;&lt;br&gt;위험도 $H = ( U - L ) / L$. 대표값 — &lt;u&gt;아세틸렌 2.5~81 [%]이므로 H = 31.4&lt;/u&gt;로 압도적으로 크고, &lt;u&gt;수소 4~75 [%] 이면 H = 17.75&lt;/u&gt;, &lt;u&gt;메탄 5~15 [%] 이면 H = 2&lt;/u&gt;다. &lt;u&gt;분모가 하한&lt;/u&gt;이라는 점 때문에 하한이 낮은 가스가 크게 유리해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$ — &lt;u&gt;분모가 하한&lt;/u&gt;이라 하한이 낮을수록 크다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 가스별 폭발범위 표는 이 책에 옮기지 못했다. 이 유형은 &lt;u&gt;식에 대입해 큰 것부터 늘어놓는&lt;/u&gt; 절차만 익히면 표가 달라져도 풀린다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12283,7 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>$2 \mathrm{Al} + 6 H_{2} O \rightarrow 2 \mathrm{Al} ( OH )_{3} + 3 H_{2}$ 로 &lt;strong&gt;수소&lt;/strong&gt;가 나온다. 수소는 폭발범위가 4~75 [%] 로 매우 넓어, 금속화재에 물을 뿌리면 불을 끄기는커녕 &lt;strong&gt;수소 폭발&lt;/strong&gt;을 부른다.</t>
+          <t>$2 \mathrm{Al} + 6 H_{2} O \rightarrow 2 \mathrm{Al} ( OH )_{3} + 3 H_{2}$로 &lt;strong&gt;수소&lt;/strong&gt;가 나온다. 수소는 폭발범위가 4~75 [%]로 매우 넓어, 금속화재에 물을 뿌리면 불을 끄기는커녕 &lt;strong&gt;수소 폭발&lt;/strong&gt;을 부른다.</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
@@ -12364,17 +12412,17 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>완전연소 조성농도 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m - 2 f - 2 l}{4} )}$ 에서 부탄은 $n = 4$, $m = 10$ 이므로 $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 6.5 ) = 3.12$ [%] 다. Jones 식은 $\mathrm{LFL} = 0.55 C_{\mathrm{st}}$ 이므로 $0.55 \times 3.12 = 1.7$ [%] 다.</t>
+          <t>완전연소 조성농도 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m - 2 f - 2 l}{4} )}$에서 부탄은 $n = 4$, $m = 10$이므로 $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 6.5 ) = 3.12$ [%]다. Jones 식은 $\mathrm{LFL} = 0.55 C_{\mathrm{st}}$이므로 $0.55 \times 3.12 = 1.7$ [%]다.</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>① 1.4 는 계수를 0.45 로 잡았을 때 나오는 값이다.&lt;br&gt;③ 2.0 은 완전연소 조성농도를 크게 잡았을 때 나온다.&lt;br&gt;④ 2.3 은 계수를 0.75 가까이 잡았을 때 나온다.</t>
+          <t>① 1.4는 계수를 0.45로 잡았을 때 나오는 값이다.&lt;br&gt;③ 2.0은 완전연소 조성농도를 크게 잡았을 때 나온다.&lt;br&gt;④ 2.3은 계수를 0.75 가까이 잡았을 때 나온다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Jones 식과 완전연소 조성농도&lt;/strong&gt;&lt;br&gt;Jones 식. &lt;u&gt;하한 &lt;/u&gt;$\mathrm{LFL} = 0.55 C_{\mathrm{st}}$, &lt;u&gt;상한 &lt;/u&gt;$\mathrm{UFL} = 3.50 C_{\mathrm{st}}$. 먼저 완전연소 조성농도를 구한 뒤 계수를 곱하는 두 단계다. 탄화수소 $C_{n} H_{m}$ 의 산소 몰수는 $n + m / 4$ 라는 것만 알면 $C_{\mathrm{st}}$ 는 바로 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한 0.55 &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt;, 상한 3.50 &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Jones 식과 완전연소 조성농도&lt;/strong&gt;&lt;br&gt;Jones 식. &lt;u&gt;하한 &lt;/u&gt;$\mathrm{LFL} = 0.55 C_{\mathrm{st}}$, &lt;u&gt;상한 &lt;/u&gt;$\mathrm{UFL} = 3.50 C_{\mathrm{st}}$. 먼저 완전연소 조성농도를 구한 뒤 계수를 곱하는 두 단계다. 탄화수소 $C_{n} H_{m}$의 산소 몰수는 $n + m / 4$라는 것만 알면 $C_{\mathrm{st}}$는 바로 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한 0.55 &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt;, 상한 3.50 &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12928,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;탄화칼슘(카바이드)&lt;/strong&gt;은 물과 만나면 $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$ 로 &lt;strong&gt;아세틸렌&lt;/strong&gt;을 내며 발열한다. 아세틸렌은 폭발범위가 2.5~81 [%] 로 대단히 넓어 곧바로 폭발로 이어진다. 그래서 &lt;strong&gt;밀폐 용기에 넣어 건조한 곳&lt;/strong&gt;에 둔다.</t>
+          <t>&lt;strong&gt;탄화칼슘(카바이드)&lt;/strong&gt;은 물과 만나면 $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$로 &lt;strong&gt;아세틸렌&lt;/strong&gt;을 내며 발열한다. 아세틸렌은 폭발범위가 2.5~81 [%]로 대단히 넓어 곧바로 폭발로 이어진다. 그래서 &lt;strong&gt;밀폐 용기에 넣어 건조한 곳&lt;/strong&gt;에 둔다.</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13143,7 +13191,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 황화수소는 허용농도 10 [ppm] 의 대표적 독성가스다. 썩은 달걀 냄새가 나지만 고농도에서는 오히려 후각이 마비된다.&lt;br&gt;② 시안화수소는 허용농도가 매우 낮은 맹독성 가스다.&lt;br&gt;④ 산화에틸렌은 독성이면서 인화성이기도 하다.</t>
+          <t>① 황화수소는 허용농도 10 [ppm]의 대표적 독성가스다. 썩은 달걀 냄새가 나지만 고농도에서는 오히려 후각이 마비된다.&lt;br&gt;② 시안화수소는 허용농도가 매우 낮은 맹독성 가스다.&lt;br&gt;④ 산화에틸렌은 독성이면서 인화성이기도 하다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13783,7 +13831,7 @@
       </c>
       <c r="AG99" s="32" t="inlineStr">
         <is>
-          <t>질화면은 &lt;strong&gt;제5류 자기반응성 물질&lt;/strong&gt;로, 분자 안에 산소를 품고 있어 &lt;strong&gt;외부 산소가 없어도 스스로 분해하며 발화&lt;/strong&gt; 한다. 건조하면 분해가 쉽게 시작되므로 알코올이나 물로 적셔 둔다.</t>
+          <t>질화면은 &lt;strong&gt;제5류 자기반응성 물질&lt;/strong&gt;로, 분자 안에 산소를 품고 있어 &lt;strong&gt;외부 산소가 없어도 스스로 분해하며 발화&lt;/strong&gt;한다. 건조하면 분해가 쉽게 시작되므로 알코올이나 물로 적셔 둔다.</t>
         </is>
       </c>
       <c r="AH99" s="32" t="inlineStr">
@@ -13793,7 +13841,7 @@
       </c>
       <c r="AI99" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제5류 자기반응성 물질&lt;/strong&gt;&lt;br&gt;분자 안에 산소를 품고 있어 &lt;strong&gt;질식소화가 통하지 않으며 다량의 물로 냉각&lt;/strong&gt; 하는 것이 원칙이다. 니트로셀룰로오스·니트로글리세린·TNT·과산화벤조일이 여기 든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 제5류는 &lt;u&gt;분자 안에 산소&lt;/u&gt; — 습면 상태를 지킨다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 선택지 ③④가 조판 과정에서 다른 문항의 것과 뒤섞여 있었다. 원문(③ 산소와 환원반응, ④ 유독한 중합물)으로 되돌려 실었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제5류 자기반응성 물질&lt;/strong&gt;&lt;br&gt;분자 안에 산소를 품고 있어 &lt;strong&gt;질식소화가 통하지 않으며 다량의 물로 냉각&lt;/strong&gt;하는 것이 원칙이다. 니트로셀룰로오스·니트로글리세린·TNT·과산화벤조일이 여기 든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 제5류는 &lt;u&gt;분자 안에 산소&lt;/u&gt; — 습면 상태를 지킨다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항의 선택지 ③④가 조판 과정에서 다른 문항의 것과 뒤섞여 있었다. 원문(③ 산소와 환원반응, ④ 유독한 중합물)으로 되돌려 실었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14187,11 @@
           <t>다음 표와 같은 혼합가스의 폭발범위(vol%)로 옳은 것은?</t>
         </is>
       </c>
-      <c r="V102" s="32" t="inlineStr"/>
+      <c r="V102" s="32" t="inlineStr">
+        <is>
+          <t>CH₄   : 용적비율 70 [%] · 폭발하한계 5 [%] · 폭발상한계 15 [%]&lt;br&gt;C₂H₆  : 용적비율 15 [%] · 폭발하한계 3 [%] · 폭발상한계 12.5 [%]&lt;br&gt;C₃H₈  : 용적비율 5 [%] · 폭발하한계 2.1 [%] · 폭발상한계 9.5 [%]&lt;br&gt;C₄H₁₀ : 용적비율 10 [%] · 폭발하한계 1.9 [%] · 폭발상한계 8.5 [%]</t>
+        </is>
+      </c>
       <c r="W102" s="32" t="inlineStr"/>
       <c r="X102" s="32" t="inlineStr">
         <is>
@@ -14170,7 +14222,7 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>하한과 상한을 각각 &lt;strong&gt;르 샤틀리에 식&lt;/strong&gt;으로 따로 구한다. $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 로 하한을, $\dfrac{100}{U} = \sum \dfrac{V_{i}}{U_{i}}$ 로 상한을 구하면 &lt;strong&gt;3.75 ~ 13.21 [%]&lt;/strong&gt;가 나온다.</t>
+          <t>하한과 상한을 각각 &lt;strong&gt;르 샤틀리에 식&lt;/strong&gt;으로 따로 구한다. $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$로 하한을, $\dfrac{100}{U} = \sum \dfrac{V_{i}}{U_{i}}$로 상한을 구하면 &lt;strong&gt;3.75 ~ 13.21 [%]&lt;/strong&gt;가 나온다.</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
@@ -14299,12 +14351,12 @@
       </c>
       <c r="AG103" s="32" t="inlineStr">
         <is>
-          <t>소선 절단 기준은 &lt;strong&gt;한 꼬임에서 10 [%] 이상&lt;/strong&gt;이다. 7 [%] 가 아니다. &lt;strong&gt;지름 감소는 7 [%] 초과, 소선 절단은 10 [%] 이상&lt;/strong&gt;으로 두 숫자가 서로 다른데, 이를 바꿔 놓는 것이 자주 나오는 함정이다.</t>
+          <t>소선 절단 기준은 &lt;strong&gt;한 꼬임에서 10 [%] 이상&lt;/strong&gt;이다. 7 [%]가 아니다. &lt;strong&gt;지름 감소는 7 [%] 초과, 소선 절단은 10 [%] 이상&lt;/strong&gt;으로 두 숫자가 서로 다른데, 이를 바꿔 놓는 것이 자주 나오는 함정이다.</t>
         </is>
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 이음매가 있는 것은 쓸 수 없다.&lt;br&gt;② 열과 전기 충격으로 손상된 것도 쓸 수 없다.&lt;br&gt;③ 지름 감소가 공칭지름의 7 [%] 를 초과하면 쓸 수 없다.</t>
+          <t>① 이음매가 있는 것은 쓸 수 없다.&lt;br&gt;② 열과 전기 충격으로 손상된 것도 쓸 수 없다.&lt;br&gt;③ 지름 감소가 공칭지름의 7 [%]를 초과하면 쓸 수 없다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14428,7 +14480,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>하역운반기계용 출입구에는 &lt;strong&gt;보행자용 출입구를 따로 설치&lt;/strong&gt; 해야 한다. 사람과 기계가 같은 문을 쓰면 충돌은 시간 문제다. &lt;strong&gt;사람과 차를 분리&lt;/strong&gt; 하는 것이 통로 안전의 기본 원칙이다.</t>
+          <t>하역운반기계용 출입구에는 &lt;strong&gt;보행자용 출입구를 따로 설치&lt;/strong&gt;해야 한다. 사람과 기계가 같은 문을 쓰면 충돌은 시간 문제다. &lt;strong&gt;사람과 차를 분리&lt;/strong&gt;하는 것이 통로 안전의 기본 원칙이다.</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14557,7 +14609,7 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>높이가 20 [m] 를 초과하거나 중량물 적재를 수반하는 작업을 할 때는 주틀 간의 간격을 &lt;strong&gt;1.8 [m] 이하&lt;/strong&gt;로 해야 한다. 2.4 [m] 가 아니다. 조건이 가혹할수록 간격을 &lt;strong&gt;좁혀야&lt;/strong&gt; 한다는 방향으로 생각하면 된다.</t>
+          <t>높이가 20 [m]를 초과하거나 중량물 적재를 수반하는 작업을 할 때는 주틀 간의 간격을 &lt;strong&gt;1.8 [m] 이하&lt;/strong&gt;로 해야 한다. 2.4 [m]가 아니다. 조건이 가혹할수록 간격을 &lt;strong&gt;좁혀야&lt;/strong&gt; 한다는 방향으로 생각하면 된다.</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
@@ -14691,7 +14743,7 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 60 [kg] 은 그물코 5 [cm] 매듭방망의 &lt;strong&gt;폐기 시&lt;/strong&gt; 기준이다.&lt;br&gt;③ 150 [kg] 은 그물코 10 [cm] 매듭방망의 폐기 시 기준이다.&lt;br&gt;④ 200 [kg] 은 그물코 10 [cm] &lt;strong&gt;매듭 없는&lt;/strong&gt; 방망의 신품 기준이다.</t>
+          <t>① 60 [kg]은 그물코 5 [cm] 매듭방망의 &lt;strong&gt;폐기 시&lt;/strong&gt; 기준이다.&lt;br&gt;③ 150 [kg]은 그물코 10 [cm] 매듭방망의 폐기 시 기준이다.&lt;br&gt;④ 200 [kg]은 그물코 10 [cm] &lt;strong&gt;매듭 없는&lt;/strong&gt; 방망의 신품 기준이다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
@@ -15202,12 +15254,12 @@
       </c>
       <c r="AG110" s="32" t="inlineStr">
         <is>
-          <t>순간풍속이 &lt;strong&gt;초당 35 [m] 를 초과&lt;/strong&gt; 할 우려가 있으면 받침의 수를 늘리는 등 붕괴 방지 조치를 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;순간풍속에 따른 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;풍속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근거&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;10 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;설치·수리·점검·해체&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;15 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;운전작업&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;30 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;옥외 주행크레인 &lt;u&gt;이탈방지장치&lt;/u&gt; 작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제140조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;35 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건설용 리프트 &lt;u&gt;붕괴 방지&lt;/u&gt; 조치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제154조&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_108_exp1.png"&gt;&lt;em&gt;강풍 시 조치 기준 — 작업 중지는 낮은 값, 구조물 보호는 높은 값&lt;/em&gt;</t>
+          <t>순간풍속이 &lt;strong&gt;초당 35 [m]를 초과&lt;/strong&gt;할 우려가 있으면 받침의 수를 늘리는 등 붕괴 방지 조치를 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;순간풍속에 따른 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;풍속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근거&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;10 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;설치·수리·점검·해체&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;15 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;운전작업&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;30 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;옥외 주행크레인 &lt;u&gt;이탈방지장치&lt;/u&gt; 작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제140조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;35 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건설용 리프트 &lt;u&gt;붕괴 방지&lt;/u&gt; 조치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제154조&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_108_exp1.png"&gt;&lt;em&gt;강풍 시 조치 기준 — 작업 중지는 낮은 값, 구조물 보호는 높은 값&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH110" s="32" t="inlineStr">
         <is>
-          <t>① 초당 15 [m] 는 타워크레인 &lt;strong&gt;운전작업 중지&lt;/strong&gt; 기준이다.&lt;br&gt;② 초당 25 [m] 라는 기준은 없다.&lt;br&gt;④ 초당 45 [m] 라는 기준은 없다.</t>
+          <t>① 초당 15 [m]는 타워크레인 &lt;strong&gt;운전작업 중지&lt;/strong&gt; 기준이다.&lt;br&gt;② 초당 25 [m]라는 기준은 없다.&lt;br&gt;④ 초당 45 [m]라는 기준은 없다.</t>
         </is>
       </c>
       <c r="AI110" s="32" t="inlineStr">
@@ -15718,7 +15770,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>이동식 비계 작업발판의 최대적재하중은 &lt;strong&gt;250 [kg] 을 초과하지 않도록&lt;/strong&gt; 한다. 400 [kg] 은 &lt;strong&gt;강관비계의 비계기둥 간 적재하중&lt;/strong&gt; 기준이라 서로 다른 값이다.</t>
+          <t>이동식 비계 작업발판의 최대적재하중은 &lt;strong&gt;250 [kg]을 초과하지 않도록&lt;/strong&gt; 한다. 400 [kg]은 &lt;strong&gt;강관비계의 비계기둥 간 적재하중&lt;/strong&gt; 기준이라 서로 다른 값이다.</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15857,7 +15909,7 @@
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가설공사 표준안전작업지침 — 통로발판&lt;/strong&gt;&lt;br&gt;발판 관련 숫자. &lt;u&gt;작업발판 폭 40 [cm] 이상(달비계는 20 [cm] 이상) · 발판재료 간 틈 3 [cm] 이하 · 통로발판 최대폭 1.6 [m] 이내 · 겹침이음 20 [cm] 이상&lt;/u&gt;. 「&lt;u&gt;40 과 3&lt;/u&gt;」, 「&lt;u&gt;1.6 과 20&lt;/u&gt;」을 각각 묶어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭 40 · 틈 3&lt;/u&gt;, 통로발판 &lt;u&gt;최대폭 1.6 [m] · 겹침 20 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가설공사 표준안전작업지침 — 통로발판&lt;/strong&gt;&lt;br&gt;발판 관련 숫자. &lt;u&gt;작업발판 폭 40 [cm] 이상(달비계는 20 [cm] 이상) · 발판재료 간 틈 3 [cm] 이하 · 통로발판 최대폭 1.6 [m] 이내 · 겹침이음 20 [cm] 이상&lt;/u&gt;. 「&lt;u&gt;40과 3&lt;/u&gt;」, 「&lt;u&gt;1.6과 20&lt;/u&gt;」을 각각 묶어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭 40 · 틈 3&lt;/u&gt;, 통로발판 &lt;u&gt;최대폭 1.6 [m] · 겹침 20 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16492,12 +16544,12 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>순간풍속이 &lt;strong&gt;초당 30 [m] 를 초과&lt;/strong&gt; 할 우려가 있으면 옥외 주행크레인의 이탈방지장치를 작동시킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;순간풍속에 따른 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;풍속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근거&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;10 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;설치·수리·점검·해체&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;15 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;운전작업&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/s] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥외 주행크레인 이탈방지장치&lt;/u&gt; 작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제140조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;35 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건설용 리프트 &lt;u&gt;붕괴 방지&lt;/u&gt; 조치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제154조&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_118_exp1.png"&gt;&lt;em&gt;강풍 시 조치 기준 — 작업 중지는 낮은 값, 구조물 보호는 높은 값&lt;/em&gt;</t>
+          <t>순간풍속이 &lt;strong&gt;초당 30 [m]를 초과&lt;/strong&gt;할 우려가 있으면 옥외 주행크레인의 이탈방지장치를 작동시킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;순간풍속에 따른 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;풍속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근거&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;10 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;설치·수리·점검·해체&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;15 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;타워크레인 &lt;u&gt;운전작업&lt;/u&gt; 중지&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제37조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/s] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥외 주행크레인 이탈방지장치&lt;/u&gt; 작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제140조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;35 [m/s] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건설용 리프트 &lt;u&gt;붕괴 방지&lt;/u&gt; 조치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규칙 제154조&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_01_118_exp1.png"&gt;&lt;em&gt;강풍 시 조치 기준 — 작업 중지는 낮은 값, 구조물 보호는 높은 값&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
         <is>
-          <t>① 초당 10 [m] 는 타워크레인 설치·해체 중지 기준이다.&lt;br&gt;② 초당 20 [m] 라는 기준은 없다.&lt;br&gt;④ 초당 40 [m] 라는 기준도 없다.</t>
+          <t>① 초당 10 [m]는 타워크레인 설치·해체 중지 기준이다.&lt;br&gt;② 초당 20 [m]라는 기준은 없다.&lt;br&gt;④ 초당 40 [m]라는 기준도 없다.</t>
         </is>
       </c>
       <c r="AI120" s="32" t="inlineStr">
